--- a/research/traditional_assets/database/data/malaysia/malaysia_air_transport.xlsx
+++ b/research/traditional_assets/database/data/malaysia/malaysia_air_transport.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="klse_airport" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,43 +590,43 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.267</v>
+        <v>-0.1036</v>
       </c>
       <c r="G2">
-        <v>-2.320783557270187</v>
+        <v>3.960980966325037</v>
       </c>
       <c r="H2">
-        <v>-2.320872688572569</v>
+        <v>3.960862709764613</v>
       </c>
       <c r="I2">
-        <v>-2.396567779699348</v>
+        <v>3.798625971393175</v>
       </c>
       <c r="J2">
-        <v>-2.396567779699348</v>
+        <v>3.798625971393175</v>
       </c>
       <c r="K2">
-        <v>-6841.8</v>
+        <v>6277.9</v>
       </c>
       <c r="L2">
-        <v>-9.101769322868165</v>
+        <v>3.535251717535759</v>
       </c>
       <c r="M2">
-        <v>13.7</v>
+        <v>12.4</v>
       </c>
       <c r="N2">
-        <v>0.004301142785382393</v>
+        <v>0.003957994190685946</v>
       </c>
       <c r="O2">
-        <v>-0.002002397030021339</v>
+        <v>0.001975182784051992</v>
       </c>
       <c r="P2">
-        <v>13.7</v>
+        <v>12.4</v>
       </c>
       <c r="Q2">
-        <v>0.004301142785382393</v>
+        <v>0.003957994190685946</v>
       </c>
       <c r="R2">
-        <v>-0.002002397030021339</v>
+        <v>0.001975182784051992</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,73 +635,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>352.55</v>
+        <v>484.12</v>
       </c>
       <c r="V2">
-        <v>0.1106837875172674</v>
+        <v>0.1545277538382968</v>
       </c>
       <c r="W2">
-        <v>-0.1483386822729847</v>
+        <v>-0.03738738738738739</v>
       </c>
       <c r="X2">
-        <v>0.2459875099714552</v>
+        <v>0.1264069388430263</v>
       </c>
       <c r="Y2">
-        <v>-0.3943261922444399</v>
+        <v>-0.1637943262304137</v>
       </c>
       <c r="Z2">
-        <v>0.1044056779354982</v>
+        <v>0.3266980646110825</v>
       </c>
       <c r="AA2">
-        <v>-0.3540489642184558</v>
+        <v>0.07575073379995484</v>
       </c>
       <c r="AB2">
-        <v>0.06573322343147069</v>
+        <v>0.1001080018070864</v>
       </c>
       <c r="AC2">
-        <v>-0.4197821876499265</v>
+        <v>-0.02204173852682287</v>
       </c>
       <c r="AD2">
-        <v>6401.4</v>
+        <v>5230.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>6401.4</v>
+        <v>5230.6</v>
       </c>
       <c r="AG2">
-        <v>6048.849999999999</v>
+        <v>4746.48</v>
       </c>
       <c r="AH2">
-        <v>0.6677445601151607</v>
+        <v>0.6254080229568961</v>
       </c>
       <c r="AI2">
-        <v>-4.927944572748268</v>
+        <v>1.227379388023278</v>
       </c>
       <c r="AJ2">
-        <v>0.6550592643531278</v>
+        <v>0.6023925740350129</v>
       </c>
       <c r="AK2">
-        <v>-3.66252913929339</v>
+        <v>1.256520219829092</v>
       </c>
       <c r="AL2">
-        <v>423.2</v>
+        <v>331.6</v>
       </c>
       <c r="AM2">
-        <v>386.6</v>
+        <v>299.318</v>
       </c>
       <c r="AN2">
-        <v>-3.95832302745486</v>
+        <v>-35.89979409746054</v>
       </c>
       <c r="AO2">
-        <v>-4.256852551984878</v>
+        <v>20.34258142340169</v>
       </c>
       <c r="AP2">
-        <v>-3.740322780113777</v>
+        <v>-32.57707618393961</v>
       </c>
       <c r="AQ2">
-        <v>-4.659855147439214</v>
+        <v>22.53656646108821</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +712,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Malaysia Airports Holdings Berhad (KLSE:AIRPORT)</t>
+          <t>AirAsia X Berhad (KLSE:AAX)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -718,119 +720,95 @@
           <t>Air Transport</t>
         </is>
       </c>
-      <c r="D3">
-        <v>-0.196</v>
-      </c>
       <c r="G3">
-        <v>-0.153683574879227</v>
+        <v>78.86575052854123</v>
       </c>
       <c r="H3">
-        <v>-0.153683574879227</v>
+        <v>78.86575052854123</v>
       </c>
       <c r="I3">
-        <v>-0.6657608695652174</v>
+        <v>74.92706131078225</v>
       </c>
       <c r="J3">
-        <v>-0.6657608695652174</v>
+        <v>74.92706131078225</v>
       </c>
       <c r="K3">
-        <v>-314.3</v>
+        <v>7095.9</v>
       </c>
       <c r="L3">
-        <v>-0.9489734299516909</v>
+        <v>75.00951374207189</v>
       </c>
       <c r="M3">
-        <v>13.7</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.00575291845133115</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0.04358892777601018</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>13.7</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.00575291845133115</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0.04358892777601018</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>253.6</v>
+        <v>5.12</v>
       </c>
       <c r="V3">
-        <v>0.1064919795078525</v>
+        <v>0.09481481481481481</v>
       </c>
       <c r="W3">
-        <v>-0.1483386822729847</v>
+        <v>-0.8798497191533683</v>
       </c>
       <c r="X3">
-        <v>0.08158650611989385</v>
+        <v>0.1001080018070864</v>
       </c>
       <c r="Y3">
-        <v>-0.2299251883928785</v>
-      </c>
-      <c r="Z3">
-        <v>0.1104073604906994</v>
-      </c>
-      <c r="AA3">
-        <v>-0.07350490032668844</v>
+        <v>-0.9799577209604546</v>
       </c>
       <c r="AB3">
-        <v>0.06348395257006446</v>
-      </c>
-      <c r="AC3">
-        <v>-0.1369888528967529</v>
+        <v>0.1001080018070864</v>
       </c>
       <c r="AD3">
-        <v>1135</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1135</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>881.4</v>
+        <v>-5.12</v>
       </c>
       <c r="AH3">
-        <v>0.322773290865658</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.3899003778770182</v>
+        <v>-0</v>
       </c>
       <c r="AJ3">
-        <v>0.2701360794409709</v>
+        <v>-0.104746317512275</v>
       </c>
       <c r="AK3">
-        <v>0.331677579589072</v>
+        <v>0.03067337646776899</v>
       </c>
       <c r="AL3">
-        <v>152.6</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>139.4</v>
-      </c>
-      <c r="AN3">
-        <v>-13.96063960639606</v>
-      </c>
-      <c r="AO3">
-        <v>-1.444954128440367</v>
-      </c>
-      <c r="AP3">
-        <v>-10.84132841328413</v>
+        <v>-0.082</v>
       </c>
       <c r="AQ3">
-        <v>-1.581779053084649</v>
+        <v>-86440.24390243902</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +819,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AirAsia Group Berhad (KLSE:AIRASIA)</t>
+          <t>Malaysia Airports Holdings Berhad (KLSE:AIRPORT)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -850,115 +828,118 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.338</v>
+        <v>-0.09820000000000001</v>
       </c>
       <c r="G4">
-        <v>-5.461104702750665</v>
+        <v>0.3875282265068612</v>
       </c>
       <c r="H4">
-        <v>-5.461401952085182</v>
+        <v>0.3875282265068612</v>
       </c>
       <c r="I4">
-        <v>-4.921029281277729</v>
+        <v>0.3496612819176654</v>
       </c>
       <c r="J4">
-        <v>-4.921029281277729</v>
+        <v>0.3496612819176654</v>
       </c>
       <c r="K4">
-        <v>-1121.3</v>
+        <v>-66.40000000000001</v>
       </c>
       <c r="L4">
-        <v>-4.974711623779946</v>
+        <v>-0.1153378495744311</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>12.4</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.004989939637826962</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>-0.1867469879518072</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>12.4</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.004989939637826962</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>-0.1867469879518072</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>95.8</v>
+        <v>389.6</v>
       </c>
       <c r="V4">
-        <v>0.1296171018806657</v>
+        <v>0.1567806841046278</v>
       </c>
       <c r="W4">
-        <v>-3.933005962820063</v>
+        <v>-0.03738738738738739</v>
       </c>
       <c r="X4">
-        <v>0.2459875099714552</v>
+        <v>0.1264069388430263</v>
       </c>
       <c r="Y4">
-        <v>-4.178993472791518</v>
+        <v>-0.1637943262304137</v>
       </c>
       <c r="Z4">
-        <v>0.0719461202081139</v>
+        <v>0.2166403251298261</v>
       </c>
       <c r="AA4">
-        <v>-0.3540489642184558</v>
+        <v>0.07575073379995484</v>
       </c>
       <c r="AB4">
-        <v>0.06573322343147069</v>
+        <v>0.09779247232677771</v>
       </c>
       <c r="AC4">
-        <v>-0.4197821876499265</v>
+        <v>-0.02204173852682287</v>
       </c>
       <c r="AD4">
-        <v>3628</v>
+        <v>1402.6</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>3628</v>
+        <v>1402.6</v>
       </c>
       <c r="AG4">
-        <v>3532.2</v>
+        <v>1013</v>
       </c>
       <c r="AH4">
-        <v>0.8307572530970209</v>
+        <v>0.3607881469286964</v>
       </c>
       <c r="AI4">
-        <v>1.636814798105121</v>
+        <v>0.4804411865451805</v>
       </c>
       <c r="AJ4">
-        <v>0.8269613466626085</v>
+        <v>0.2895940537449971</v>
       </c>
       <c r="AK4">
-        <v>1.665582119111614</v>
+        <v>0.4004269112182781</v>
       </c>
       <c r="AL4">
-        <v>146.9</v>
+        <v>149.7</v>
       </c>
       <c r="AM4">
-        <v>136.1</v>
+        <v>130.2</v>
       </c>
       <c r="AN4">
-        <v>-3.380544166977264</v>
+        <v>3.85541506322155</v>
       </c>
       <c r="AO4">
-        <v>-7.55071477195371</v>
+        <v>1.344689378757515</v>
       </c>
       <c r="AP4">
-        <v>-3.291278419679463</v>
+        <v>2.784496976360638</v>
       </c>
       <c r="AQ4">
-        <v>-8.149889786921381</v>
+        <v>1.546082949308756</v>
       </c>
     </row>
     <row r="5">
@@ -969,7 +950,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AirAsia X Berhad (KLSE:AAX)</t>
+          <t>Capital A Berhad (KLSE:CAPITALA)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -977,23 +958,26 @@
           <t>Air Transport</t>
         </is>
       </c>
+      <c r="D5">
+        <v>-0.109</v>
+      </c>
       <c r="G5">
-        <v>-2.371604305484367</v>
+        <v>-0.5878697421981004</v>
       </c>
       <c r="H5">
-        <v>-2.371604305484367</v>
+        <v>-0.5880597014925373</v>
       </c>
       <c r="I5">
-        <v>-2.418247052793439</v>
+        <v>-0.4919041157847128</v>
       </c>
       <c r="J5">
-        <v>-2.418247052793439</v>
+        <v>-0.4919041157847128</v>
       </c>
       <c r="K5">
-        <v>-5406.2</v>
+        <v>-751.6</v>
       </c>
       <c r="L5">
-        <v>-27.70989236289083</v>
+        <v>-0.6798733604703754</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1017,73 +1001,8785 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>3.15</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="V5">
-        <v>0.04868624420401854</v>
+        <v>0.1505303923219397</v>
       </c>
       <c r="W5">
-        <v>19.52401589021308</v>
+        <v>0.996816976127321</v>
       </c>
       <c r="X5">
-        <v>1.003228832498331</v>
+        <v>0.4004315301743542</v>
       </c>
       <c r="Y5">
-        <v>18.52078705771475</v>
+        <v>0.5963854459529668</v>
       </c>
       <c r="Z5">
-        <v>0.1828319745103552</v>
+        <v>0.3979195162335326</v>
       </c>
       <c r="AA5">
-        <v>-0.4421328835160717</v>
+        <v>-0.1957382477863365</v>
       </c>
       <c r="AB5">
-        <v>0.06824924481120462</v>
+        <v>0.1021181580440427</v>
       </c>
       <c r="AC5">
-        <v>-0.5103821283272763</v>
+        <v>-0.2978564058303792</v>
       </c>
       <c r="AD5">
-        <v>1638.4</v>
+        <v>3828</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>1638.4</v>
+        <v>3828</v>
       </c>
       <c r="AG5">
-        <v>1635.25</v>
+        <v>3738.6</v>
       </c>
       <c r="AH5">
-        <v>0.9620104515295637</v>
+        <v>0.8656912187068908</v>
       </c>
       <c r="AI5">
-        <v>-0.2549443709639773</v>
+        <v>2.545212765957447</v>
       </c>
       <c r="AJ5">
-        <v>0.9619400570605018</v>
+        <v>0.8629197922677437</v>
       </c>
       <c r="AK5">
-        <v>-0.2543295513752692</v>
+        <v>2.642867241623074</v>
       </c>
       <c r="AL5">
-        <v>123.7</v>
+        <v>181.9</v>
       </c>
       <c r="AM5">
-        <v>111.1</v>
+        <v>169.2</v>
       </c>
       <c r="AN5">
-        <v>-3.540955262589151</v>
+        <v>-7.51324828263003</v>
       </c>
       <c r="AO5">
-        <v>-3.814066289409863</v>
+        <v>-2.989554700384827</v>
       </c>
       <c r="AP5">
-        <v>-3.534147395720769</v>
+        <v>-7.337782139352306</v>
       </c>
       <c r="AQ5">
-        <v>-4.246624662466246</v>
+        <v>-3.213947990543735</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Malaysia Airports Holdings Berhad (KLSE:AIRPORT)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>KLSE:AIRPORT</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Air Transport</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.360788146928696</v>
+      </c>
+      <c r="F2">
+        <v>0.2</v>
+      </c>
+      <c r="G2">
+        <v>2485</v>
+      </c>
+      <c r="H2">
+        <v>3111.13474374091</v>
+      </c>
+      <c r="I2">
+        <v>3498</v>
+      </c>
+      <c r="J2">
+        <v>3499.05474374092</v>
+      </c>
+      <c r="K2">
+        <v>1402.6</v>
+      </c>
+      <c r="L2">
+        <v>777.52</v>
+      </c>
+      <c r="M2">
+        <v>0.09779247232677769</v>
+      </c>
+      <c r="N2">
+        <v>0.0977652177203463</v>
+      </c>
+      <c r="O2">
+        <v>0.0470959449541284</v>
+      </c>
+      <c r="P2">
+        <v>0.0418</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Caa/CCC</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.126406938843026</v>
+      </c>
+      <c r="T2">
+        <v>0.111756522150433</v>
+      </c>
+      <c r="U2">
+        <v>1.09736463809141</v>
+      </c>
+      <c r="V2">
+        <v>0.9138534981740249</v>
+      </c>
+      <c r="W2">
+        <v>4.531891608751369</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>2485</v>
+      </c>
+      <c r="AB2">
+        <v>0.07983393650755573</v>
+      </c>
+      <c r="AC2">
+        <v>0.06196834862385321</v>
+      </c>
+      <c r="AD2">
+        <v>0.24</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>363.8</v>
+      </c>
+      <c r="AH2">
+        <v>170</v>
+      </c>
+      <c r="AI2">
+        <v>3.330000000000004</v>
+      </c>
+      <c r="AJ2">
+        <v>1402.6</v>
+      </c>
+      <c r="AK2">
+        <v>1402.6</v>
+      </c>
+      <c r="AL2">
+        <v>149.7</v>
+      </c>
+      <c r="AM2">
+        <v>1402.6</v>
+      </c>
+      <c r="AN2">
+        <v>389.6</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1001080018070864</v>
+      </c>
+      <c r="C2">
+        <v>3800.253752559782</v>
+      </c>
+      <c r="D2">
+        <v>3410.653752559782</v>
+      </c>
+      <c r="E2">
+        <v>-1402.6</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>389.6</v>
+      </c>
+      <c r="H2">
+        <v>2485</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>363.8</v>
+      </c>
+      <c r="K2">
+        <v>170</v>
+      </c>
+      <c r="L2">
+        <v>193.8</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>193.8</v>
+      </c>
+      <c r="O2">
+        <v>46.512</v>
+      </c>
+      <c r="P2">
+        <v>147.288</v>
+      </c>
+      <c r="Q2">
+        <v>317.288</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1001080018070864</v>
+      </c>
+      <c r="T2">
+        <v>0.7679441161126263</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.24</v>
+      </c>
+      <c r="W2">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.0999201826027494</v>
+      </c>
+      <c r="C3">
+        <v>3768.299763468434</v>
+      </c>
+      <c r="D3">
+        <v>3417.575763468434</v>
+      </c>
+      <c r="E3">
+        <v>-1363.724</v>
+      </c>
+      <c r="F3">
+        <v>38.876</v>
+      </c>
+      <c r="G3">
+        <v>389.6</v>
+      </c>
+      <c r="H3">
+        <v>2485</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>363.8</v>
+      </c>
+      <c r="K3">
+        <v>170</v>
+      </c>
+      <c r="L3">
+        <v>193.8</v>
+      </c>
+      <c r="M3">
+        <v>1.7766332</v>
+      </c>
+      <c r="N3">
+        <v>192.0233668</v>
+      </c>
+      <c r="O3">
+        <v>46.085608032</v>
+      </c>
+      <c r="P3">
+        <v>145.937758768</v>
+      </c>
+      <c r="Q3">
+        <v>315.937758768</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1005786490936863</v>
+      </c>
+      <c r="T3">
+        <v>0.7738394446807636</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.24</v>
+      </c>
+      <c r="W3">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>109.0827301887638</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.09973236339841239</v>
+      </c>
+      <c r="C4">
+        <v>3736.373928320262</v>
+      </c>
+      <c r="D4">
+        <v>3424.525928320262</v>
+      </c>
+      <c r="E4">
+        <v>-1324.848</v>
+      </c>
+      <c r="F4">
+        <v>77.752</v>
+      </c>
+      <c r="G4">
+        <v>389.6</v>
+      </c>
+      <c r="H4">
+        <v>2485</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>363.8</v>
+      </c>
+      <c r="K4">
+        <v>170</v>
+      </c>
+      <c r="L4">
+        <v>193.8</v>
+      </c>
+      <c r="M4">
+        <v>3.5532664</v>
+      </c>
+      <c r="N4">
+        <v>190.2467336</v>
+      </c>
+      <c r="O4">
+        <v>45.659216064</v>
+      </c>
+      <c r="P4">
+        <v>144.587517536</v>
+      </c>
+      <c r="Q4">
+        <v>314.587517536</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1010589014269514</v>
+      </c>
+      <c r="T4">
+        <v>0.7798550860768221</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.24</v>
+      </c>
+      <c r="W4">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>54.54136509438189</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.09954454419407538</v>
+      </c>
+      <c r="C5">
+        <v>3704.476419231384</v>
+      </c>
+      <c r="D5">
+        <v>3431.504419231384</v>
+      </c>
+      <c r="E5">
+        <v>-1285.972</v>
+      </c>
+      <c r="F5">
+        <v>116.628</v>
+      </c>
+      <c r="G5">
+        <v>389.6</v>
+      </c>
+      <c r="H5">
+        <v>2485</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>363.8</v>
+      </c>
+      <c r="K5">
+        <v>170</v>
+      </c>
+      <c r="L5">
+        <v>193.8</v>
+      </c>
+      <c r="M5">
+        <v>5.3298996</v>
+      </c>
+      <c r="N5">
+        <v>188.4701004</v>
+      </c>
+      <c r="O5">
+        <v>45.232824096</v>
+      </c>
+      <c r="P5">
+        <v>143.237276304</v>
+      </c>
+      <c r="Q5">
+        <v>313.237276304</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1015490558701808</v>
+      </c>
+      <c r="T5">
+        <v>0.7859947613160984</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.24</v>
+      </c>
+      <c r="W5">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>36.36091006292126</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.09935672498973838</v>
+      </c>
+      <c r="C6">
+        <v>3672.607409723734</v>
+      </c>
+      <c r="D6">
+        <v>3438.511409723734</v>
+      </c>
+      <c r="E6">
+        <v>-1247.096</v>
+      </c>
+      <c r="F6">
+        <v>155.504</v>
+      </c>
+      <c r="G6">
+        <v>389.6</v>
+      </c>
+      <c r="H6">
+        <v>2485</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>363.8</v>
+      </c>
+      <c r="K6">
+        <v>170</v>
+      </c>
+      <c r="L6">
+        <v>193.8</v>
+      </c>
+      <c r="M6">
+        <v>7.1065328</v>
+      </c>
+      <c r="N6">
+        <v>186.6934672</v>
+      </c>
+      <c r="O6">
+        <v>44.806432128</v>
+      </c>
+      <c r="P6">
+        <v>141.887035072</v>
+      </c>
+      <c r="Q6">
+        <v>311.887035072</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1020494218643108</v>
+      </c>
+      <c r="T6">
+        <v>0.7922623464561928</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.24</v>
+      </c>
+      <c r="W6">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>27.27068254719095</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.09916890578540137</v>
+      </c>
+      <c r="C7">
+        <v>3640.767074739445</v>
+      </c>
+      <c r="D7">
+        <v>3445.547074739445</v>
+      </c>
+      <c r="E7">
+        <v>-1208.22</v>
+      </c>
+      <c r="F7">
+        <v>194.38</v>
+      </c>
+      <c r="G7">
+        <v>389.6</v>
+      </c>
+      <c r="H7">
+        <v>2485</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>363.8</v>
+      </c>
+      <c r="K7">
+        <v>170</v>
+      </c>
+      <c r="L7">
+        <v>193.8</v>
+      </c>
+      <c r="M7">
+        <v>8.883166000000001</v>
+      </c>
+      <c r="N7">
+        <v>184.916834</v>
+      </c>
+      <c r="O7">
+        <v>44.38004016000001</v>
+      </c>
+      <c r="P7">
+        <v>140.53679384</v>
+      </c>
+      <c r="Q7">
+        <v>310.53679384</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1025603218793699</v>
+      </c>
+      <c r="T7">
+        <v>0.7986618807571313</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.24</v>
+      </c>
+      <c r="W7">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>21.81654603775276</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.09898108658106437</v>
+      </c>
+      <c r="C8">
+        <v>3608.955590655406</v>
+      </c>
+      <c r="D8">
+        <v>3452.611590655406</v>
+      </c>
+      <c r="E8">
+        <v>-1169.344</v>
+      </c>
+      <c r="F8">
+        <v>233.256</v>
+      </c>
+      <c r="G8">
+        <v>389.6</v>
+      </c>
+      <c r="H8">
+        <v>2485</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>363.8</v>
+      </c>
+      <c r="K8">
+        <v>170</v>
+      </c>
+      <c r="L8">
+        <v>193.8</v>
+      </c>
+      <c r="M8">
+        <v>10.6597992</v>
+      </c>
+      <c r="N8">
+        <v>183.1402008</v>
+      </c>
+      <c r="O8">
+        <v>43.953648192</v>
+      </c>
+      <c r="P8">
+        <v>139.186552608</v>
+      </c>
+      <c r="Q8">
+        <v>309.186552608</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1030820921075153</v>
+      </c>
+      <c r="T8">
+        <v>0.8051975753623452</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.24</v>
+      </c>
+      <c r="W8">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>18.18045503146063</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.09879326737672735</v>
+      </c>
+      <c r="C9">
+        <v>3577.173135298009</v>
+      </c>
+      <c r="D9">
+        <v>3459.705135298009</v>
+      </c>
+      <c r="E9">
+        <v>-1130.468</v>
+      </c>
+      <c r="F9">
+        <v>272.132</v>
+      </c>
+      <c r="G9">
+        <v>389.6</v>
+      </c>
+      <c r="H9">
+        <v>2485</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>363.8</v>
+      </c>
+      <c r="K9">
+        <v>170</v>
+      </c>
+      <c r="L9">
+        <v>193.8</v>
+      </c>
+      <c r="M9">
+        <v>12.4364324</v>
+      </c>
+      <c r="N9">
+        <v>181.3635676</v>
+      </c>
+      <c r="O9">
+        <v>43.527256224</v>
+      </c>
+      <c r="P9">
+        <v>137.836311376</v>
+      </c>
+      <c r="Q9">
+        <v>307.836311376</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1036150832007821</v>
+      </c>
+      <c r="T9">
+        <v>0.8118738225397141</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.24</v>
+      </c>
+      <c r="W9">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>15.5832471698234</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.09860544817239034</v>
+      </c>
+      <c r="C10">
+        <v>3545.419887958055</v>
+      </c>
+      <c r="D10">
+        <v>3466.827887958055</v>
+      </c>
+      <c r="E10">
+        <v>-1091.592</v>
+      </c>
+      <c r="F10">
+        <v>311.008</v>
+      </c>
+      <c r="G10">
+        <v>389.6</v>
+      </c>
+      <c r="H10">
+        <v>2485</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>363.8</v>
+      </c>
+      <c r="K10">
+        <v>170</v>
+      </c>
+      <c r="L10">
+        <v>193.8</v>
+      </c>
+      <c r="M10">
+        <v>14.2130656</v>
+      </c>
+      <c r="N10">
+        <v>179.5869344</v>
+      </c>
+      <c r="O10">
+        <v>43.100864256</v>
+      </c>
+      <c r="P10">
+        <v>136.486070144</v>
+      </c>
+      <c r="Q10">
+        <v>306.486070144</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.104159661056946</v>
+      </c>
+      <c r="T10">
+        <v>0.8186952055252866</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.24</v>
+      </c>
+      <c r="W10">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>13.63534127359547</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.09852706896805334</v>
+      </c>
+      <c r="C11">
+        <v>3509.524978714588</v>
+      </c>
+      <c r="D11">
+        <v>3469.808978714588</v>
+      </c>
+      <c r="E11">
+        <v>-1052.716</v>
+      </c>
+      <c r="F11">
+        <v>349.884</v>
+      </c>
+      <c r="G11">
+        <v>389.6</v>
+      </c>
+      <c r="H11">
+        <v>2485</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>363.8</v>
+      </c>
+      <c r="K11">
+        <v>170</v>
+      </c>
+      <c r="L11">
+        <v>193.8</v>
+      </c>
+      <c r="M11">
+        <v>16.5495132</v>
+      </c>
+      <c r="N11">
+        <v>177.2504868</v>
+      </c>
+      <c r="O11">
+        <v>42.540116832</v>
+      </c>
+      <c r="P11">
+        <v>134.710369968</v>
+      </c>
+      <c r="Q11">
+        <v>304.710369968</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1047162076572015</v>
+      </c>
+      <c r="T11">
+        <v>0.8256665090160368</v>
+      </c>
+      <c r="U11">
+        <v>0.0473</v>
+      </c>
+      <c r="V11">
+        <v>0.24</v>
+      </c>
+      <c r="W11">
+        <v>0.035948</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>11.71031423449966</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.09835140976371634</v>
+      </c>
+      <c r="C12">
+        <v>3477.348693226721</v>
+      </c>
+      <c r="D12">
+        <v>3476.508693226721</v>
+      </c>
+      <c r="E12">
+        <v>-1013.84</v>
+      </c>
+      <c r="F12">
+        <v>388.76</v>
+      </c>
+      <c r="G12">
+        <v>389.6</v>
+      </c>
+      <c r="H12">
+        <v>2485</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>363.8</v>
+      </c>
+      <c r="K12">
+        <v>170</v>
+      </c>
+      <c r="L12">
+        <v>193.8</v>
+      </c>
+      <c r="M12">
+        <v>18.388348</v>
+      </c>
+      <c r="N12">
+        <v>175.411652</v>
+      </c>
+      <c r="O12">
+        <v>42.09879648</v>
+      </c>
+      <c r="P12">
+        <v>133.31285552</v>
+      </c>
+      <c r="Q12">
+        <v>303.31285552</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1052851219596848</v>
+      </c>
+      <c r="T12">
+        <v>0.832792730362137</v>
+      </c>
+      <c r="U12">
+        <v>0.0473</v>
+      </c>
+      <c r="V12">
+        <v>0.24</v>
+      </c>
+      <c r="W12">
+        <v>0.035948</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>10.53928281104969</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.09849343055937934</v>
+      </c>
+      <c r="C13">
+        <v>3433.053961749732</v>
+      </c>
+      <c r="D13">
+        <v>3471.089961749733</v>
+      </c>
+      <c r="E13">
+        <v>-974.9639999999999</v>
+      </c>
+      <c r="F13">
+        <v>427.636</v>
+      </c>
+      <c r="G13">
+        <v>389.6</v>
+      </c>
+      <c r="H13">
+        <v>2485</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>363.8</v>
+      </c>
+      <c r="K13">
+        <v>170</v>
+      </c>
+      <c r="L13">
+        <v>193.8</v>
+      </c>
+      <c r="M13">
+        <v>21.8521996</v>
+      </c>
+      <c r="N13">
+        <v>171.9478004</v>
+      </c>
+      <c r="O13">
+        <v>41.267472096</v>
+      </c>
+      <c r="P13">
+        <v>130.680328304</v>
+      </c>
+      <c r="Q13">
+        <v>300.680328304</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1058668208532352</v>
+      </c>
+      <c r="T13">
+        <v>0.8400790915137674</v>
+      </c>
+      <c r="U13">
+        <v>0.0511</v>
+      </c>
+      <c r="V13">
+        <v>0.24</v>
+      </c>
+      <c r="W13">
+        <v>0.038836</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>8.868672424170974</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.09834665135504231</v>
+      </c>
+      <c r="C14">
+        <v>3399.778540835113</v>
+      </c>
+      <c r="D14">
+        <v>3476.690540835113</v>
+      </c>
+      <c r="E14">
+        <v>-936.088</v>
+      </c>
+      <c r="F14">
+        <v>466.5119999999999</v>
+      </c>
+      <c r="G14">
+        <v>389.6</v>
+      </c>
+      <c r="H14">
+        <v>2485</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>363.8</v>
+      </c>
+      <c r="K14">
+        <v>170</v>
+      </c>
+      <c r="L14">
+        <v>193.8</v>
+      </c>
+      <c r="M14">
+        <v>23.8387632</v>
+      </c>
+      <c r="N14">
+        <v>169.9612368</v>
+      </c>
+      <c r="O14">
+        <v>40.790696832</v>
+      </c>
+      <c r="P14">
+        <v>129.170539968</v>
+      </c>
+      <c r="Q14">
+        <v>299.170539968</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1064617401761844</v>
+      </c>
+      <c r="T14">
+        <v>0.8475310517824801</v>
+      </c>
+      <c r="U14">
+        <v>0.0511</v>
+      </c>
+      <c r="V14">
+        <v>0.24</v>
+      </c>
+      <c r="W14">
+        <v>0.038836</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>8.129616388823397</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.09838759215070532</v>
+      </c>
+      <c r="C15">
+        <v>3359.338567152532</v>
+      </c>
+      <c r="D15">
+        <v>3475.126567152532</v>
+      </c>
+      <c r="E15">
+        <v>-897.2119999999999</v>
+      </c>
+      <c r="F15">
+        <v>505.388</v>
+      </c>
+      <c r="G15">
+        <v>389.6</v>
+      </c>
+      <c r="H15">
+        <v>2485</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>363.8</v>
+      </c>
+      <c r="K15">
+        <v>170</v>
+      </c>
+      <c r="L15">
+        <v>193.8</v>
+      </c>
+      <c r="M15">
+        <v>26.785564</v>
+      </c>
+      <c r="N15">
+        <v>167.014436</v>
+      </c>
+      <c r="O15">
+        <v>40.08346464</v>
+      </c>
+      <c r="P15">
+        <v>126.93097136</v>
+      </c>
+      <c r="Q15">
+        <v>296.93097136</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1070703358054084</v>
+      </c>
+      <c r="T15">
+        <v>0.8551543214826579</v>
+      </c>
+      <c r="U15">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V15">
+        <v>0.24</v>
+      </c>
+      <c r="W15">
+        <v>0.04028</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>7.235240594523229</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.0982552529463683</v>
+      </c>
+      <c r="C16">
+        <v>3325.523123222333</v>
+      </c>
+      <c r="D16">
+        <v>3480.187123222333</v>
+      </c>
+      <c r="E16">
+        <v>-858.3359999999999</v>
+      </c>
+      <c r="F16">
+        <v>544.264</v>
+      </c>
+      <c r="G16">
+        <v>389.6</v>
+      </c>
+      <c r="H16">
+        <v>2485</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>363.8</v>
+      </c>
+      <c r="K16">
+        <v>170</v>
+      </c>
+      <c r="L16">
+        <v>193.8</v>
+      </c>
+      <c r="M16">
+        <v>28.845992</v>
+      </c>
+      <c r="N16">
+        <v>164.954008</v>
+      </c>
+      <c r="O16">
+        <v>39.58896192</v>
+      </c>
+      <c r="P16">
+        <v>125.36504608</v>
+      </c>
+      <c r="Q16">
+        <v>295.36504608</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1076930848213585</v>
+      </c>
+      <c r="T16">
+        <v>0.8629548765247</v>
+      </c>
+      <c r="U16">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V16">
+        <v>0.24</v>
+      </c>
+      <c r="W16">
+        <v>0.04028</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>6.718437694914427</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.09812291374203129</v>
+      </c>
+      <c r="C17">
+        <v>3291.722439373156</v>
+      </c>
+      <c r="D17">
+        <v>3485.262439373156</v>
+      </c>
+      <c r="E17">
+        <v>-819.4599999999999</v>
+      </c>
+      <c r="F17">
+        <v>583.14</v>
+      </c>
+      <c r="G17">
+        <v>389.6</v>
+      </c>
+      <c r="H17">
+        <v>2485</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>363.8</v>
+      </c>
+      <c r="K17">
+        <v>170</v>
+      </c>
+      <c r="L17">
+        <v>193.8</v>
+      </c>
+      <c r="M17">
+        <v>30.90642</v>
+      </c>
+      <c r="N17">
+        <v>162.89358</v>
+      </c>
+      <c r="O17">
+        <v>39.0944592</v>
+      </c>
+      <c r="P17">
+        <v>123.7991208</v>
+      </c>
+      <c r="Q17">
+        <v>293.7991208</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1083304867553309</v>
+      </c>
+      <c r="T17">
+        <v>0.8709389740383195</v>
+      </c>
+      <c r="U17">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V17">
+        <v>0.24</v>
+      </c>
+      <c r="W17">
+        <v>0.04028</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>6.270541848586798</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.09823377453769429</v>
+      </c>
+      <c r="C18">
+        <v>3248.593832598468</v>
+      </c>
+      <c r="D18">
+        <v>3481.009832598469</v>
+      </c>
+      <c r="E18">
+        <v>-780.5839999999999</v>
+      </c>
+      <c r="F18">
+        <v>622.016</v>
+      </c>
+      <c r="G18">
+        <v>389.6</v>
+      </c>
+      <c r="H18">
+        <v>2485</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>363.8</v>
+      </c>
+      <c r="K18">
+        <v>170</v>
+      </c>
+      <c r="L18">
+        <v>193.8</v>
+      </c>
+      <c r="M18">
+        <v>34.21088</v>
+      </c>
+      <c r="N18">
+        <v>159.58912</v>
+      </c>
+      <c r="O18">
+        <v>38.3013888</v>
+      </c>
+      <c r="P18">
+        <v>121.2877312</v>
+      </c>
+      <c r="Q18">
+        <v>291.2877312</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1089830649258265</v>
+      </c>
+      <c r="T18">
+        <v>0.8791131691117875</v>
+      </c>
+      <c r="U18">
+        <v>0.055</v>
+      </c>
+      <c r="V18">
+        <v>0.24</v>
+      </c>
+      <c r="W18">
+        <v>0.0418</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>5.664864510939211</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.09811663533335728</v>
+      </c>
+      <c r="C19">
+        <v>3214.211589281454</v>
+      </c>
+      <c r="D19">
+        <v>3485.503589281454</v>
+      </c>
+      <c r="E19">
+        <v>-741.7079999999999</v>
+      </c>
+      <c r="F19">
+        <v>660.8920000000001</v>
+      </c>
+      <c r="G19">
+        <v>389.6</v>
+      </c>
+      <c r="H19">
+        <v>2485</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>363.8</v>
+      </c>
+      <c r="K19">
+        <v>170</v>
+      </c>
+      <c r="L19">
+        <v>193.8</v>
+      </c>
+      <c r="M19">
+        <v>36.34906</v>
+      </c>
+      <c r="N19">
+        <v>157.45094</v>
+      </c>
+      <c r="O19">
+        <v>37.7882256</v>
+      </c>
+      <c r="P19">
+        <v>119.6627144</v>
+      </c>
+      <c r="Q19">
+        <v>289.6627144</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1096513678715148</v>
+      </c>
+      <c r="T19">
+        <v>0.8874843327412423</v>
+      </c>
+      <c r="U19">
+        <v>0.055</v>
+      </c>
+      <c r="V19">
+        <v>0.24</v>
+      </c>
+      <c r="W19">
+        <v>0.0418</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>5.331637186766315</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.09799949612902029</v>
+      </c>
+      <c r="C20">
+        <v>3179.840963255246</v>
+      </c>
+      <c r="D20">
+        <v>3490.008963255246</v>
+      </c>
+      <c r="E20">
+        <v>-702.832</v>
+      </c>
+      <c r="F20">
+        <v>699.7679999999999</v>
+      </c>
+      <c r="G20">
+        <v>389.6</v>
+      </c>
+      <c r="H20">
+        <v>2485</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>363.8</v>
+      </c>
+      <c r="K20">
+        <v>170</v>
+      </c>
+      <c r="L20">
+        <v>193.8</v>
+      </c>
+      <c r="M20">
+        <v>38.48723999999999</v>
+      </c>
+      <c r="N20">
+        <v>155.31276</v>
+      </c>
+      <c r="O20">
+        <v>37.2750624</v>
+      </c>
+      <c r="P20">
+        <v>118.0376976</v>
+      </c>
+      <c r="Q20">
+        <v>288.0376976</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1103359708890491</v>
+      </c>
+      <c r="T20">
+        <v>0.8960596710933668</v>
+      </c>
+      <c r="U20">
+        <v>0.055</v>
+      </c>
+      <c r="V20">
+        <v>0.24</v>
+      </c>
+      <c r="W20">
+        <v>0.0418</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>5.035435120834855</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.09788235692468326</v>
+      </c>
+      <c r="C21">
+        <v>3145.481999627804</v>
+      </c>
+      <c r="D21">
+        <v>3494.525999627804</v>
+      </c>
+      <c r="E21">
+        <v>-663.9559999999999</v>
+      </c>
+      <c r="F21">
+        <v>738.644</v>
+      </c>
+      <c r="G21">
+        <v>389.6</v>
+      </c>
+      <c r="H21">
+        <v>2485</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>363.8</v>
+      </c>
+      <c r="K21">
+        <v>170</v>
+      </c>
+      <c r="L21">
+        <v>193.8</v>
+      </c>
+      <c r="M21">
+        <v>40.62542</v>
+      </c>
+      <c r="N21">
+        <v>153.17458</v>
+      </c>
+      <c r="O21">
+        <v>36.7618992</v>
+      </c>
+      <c r="P21">
+        <v>116.4126808</v>
+      </c>
+      <c r="Q21">
+        <v>286.4126808</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1110374776847941</v>
+      </c>
+      <c r="T21">
+        <v>0.9048467461949264</v>
+      </c>
+      <c r="U21">
+        <v>0.055</v>
+      </c>
+      <c r="V21">
+        <v>0.24</v>
+      </c>
+      <c r="W21">
+        <v>0.0418</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>4.770412219738283</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.09776521772034627</v>
+      </c>
+      <c r="C22">
+        <v>3111.134743740915</v>
+      </c>
+      <c r="D22">
+        <v>3499.054743740915</v>
+      </c>
+      <c r="E22">
+        <v>-625.0799999999999</v>
+      </c>
+      <c r="F22">
+        <v>777.52</v>
+      </c>
+      <c r="G22">
+        <v>389.6</v>
+      </c>
+      <c r="H22">
+        <v>2485</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>363.8</v>
+      </c>
+      <c r="K22">
+        <v>170</v>
+      </c>
+      <c r="L22">
+        <v>193.8</v>
+      </c>
+      <c r="M22">
+        <v>42.7636</v>
+      </c>
+      <c r="N22">
+        <v>151.0364</v>
+      </c>
+      <c r="O22">
+        <v>36.248736</v>
+      </c>
+      <c r="P22">
+        <v>114.787664</v>
+      </c>
+      <c r="Q22">
+        <v>284.787664</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1117565221504328</v>
+      </c>
+      <c r="T22">
+        <v>0.9138534981740252</v>
+      </c>
+      <c r="U22">
+        <v>0.055</v>
+      </c>
+      <c r="V22">
+        <v>0.24</v>
+      </c>
+      <c r="W22">
+        <v>0.0418</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>4.531891608751369</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.09825455851600925</v>
+      </c>
+      <c r="C23">
+        <v>3053.417716612703</v>
+      </c>
+      <c r="D23">
+        <v>3480.213716612703</v>
+      </c>
+      <c r="E23">
+        <v>-586.204</v>
+      </c>
+      <c r="F23">
+        <v>816.396</v>
+      </c>
+      <c r="G23">
+        <v>389.6</v>
+      </c>
+      <c r="H23">
+        <v>2485</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>363.8</v>
+      </c>
+      <c r="K23">
+        <v>170</v>
+      </c>
+      <c r="L23">
+        <v>193.8</v>
+      </c>
+      <c r="M23">
+        <v>48.0040848</v>
+      </c>
+      <c r="N23">
+        <v>145.7959152</v>
+      </c>
+      <c r="O23">
+        <v>34.99101964800001</v>
+      </c>
+      <c r="P23">
+        <v>110.804895552</v>
+      </c>
+      <c r="Q23">
+        <v>280.804895552</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1124937702734294</v>
+      </c>
+      <c r="T23">
+        <v>0.9230882691905695</v>
+      </c>
+      <c r="U23">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V23">
+        <v>0.24</v>
+      </c>
+      <c r="W23">
+        <v>0.04468800000000001</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>4.037156437987128</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.09886853931167225</v>
+      </c>
+      <c r="C24">
+        <v>2991.186772182649</v>
+      </c>
+      <c r="D24">
+        <v>3456.858772182649</v>
+      </c>
+      <c r="E24">
+        <v>-547.328</v>
+      </c>
+      <c r="F24">
+        <v>855.2719999999999</v>
+      </c>
+      <c r="G24">
+        <v>389.6</v>
+      </c>
+      <c r="H24">
+        <v>2485</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>363.8</v>
+      </c>
+      <c r="K24">
+        <v>170</v>
+      </c>
+      <c r="L24">
+        <v>193.8</v>
+      </c>
+      <c r="M24">
+        <v>53.882136</v>
+      </c>
+      <c r="N24">
+        <v>139.917864</v>
+      </c>
+      <c r="O24">
+        <v>33.58028736</v>
+      </c>
+      <c r="P24">
+        <v>106.33757664</v>
+      </c>
+      <c r="Q24">
+        <v>276.33757664</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1132499221944516</v>
+      </c>
+      <c r="T24">
+        <v>0.932559829207538</v>
+      </c>
+      <c r="U24">
+        <v>0.063</v>
+      </c>
+      <c r="V24">
+        <v>0.24</v>
+      </c>
+      <c r="W24">
+        <v>0.04788</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>3.596739372024896</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1000532801073352</v>
+      </c>
+      <c r="C25">
+        <v>2908.11960525535</v>
+      </c>
+      <c r="D25">
+        <v>3412.66760525535</v>
+      </c>
+      <c r="E25">
+        <v>-508.4519999999999</v>
+      </c>
+      <c r="F25">
+        <v>894.148</v>
+      </c>
+      <c r="G25">
+        <v>389.6</v>
+      </c>
+      <c r="H25">
+        <v>2485</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>363.8</v>
+      </c>
+      <c r="K25">
+        <v>170</v>
+      </c>
+      <c r="L25">
+        <v>193.8</v>
+      </c>
+      <c r="M25">
+        <v>62.6797748</v>
+      </c>
+      <c r="N25">
+        <v>131.1202252</v>
+      </c>
+      <c r="O25">
+        <v>31.468854048</v>
+      </c>
+      <c r="P25">
+        <v>99.65137115200002</v>
+      </c>
+      <c r="Q25">
+        <v>269.651371152</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1140257144251107</v>
+      </c>
+      <c r="T25">
+        <v>0.9422774037704017</v>
+      </c>
+      <c r="U25">
+        <v>0.0701</v>
+      </c>
+      <c r="V25">
+        <v>0.24</v>
+      </c>
+      <c r="W25">
+        <v>0.053276</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>3.091906450180801</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1039360209029982</v>
+      </c>
+      <c r="C26">
+        <v>2732.016894017223</v>
+      </c>
+      <c r="D26">
+        <v>3275.440894017222</v>
+      </c>
+      <c r="E26">
+        <v>-469.576</v>
+      </c>
+      <c r="F26">
+        <v>933.0239999999999</v>
+      </c>
+      <c r="G26">
+        <v>389.6</v>
+      </c>
+      <c r="H26">
+        <v>2485</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>363.8</v>
+      </c>
+      <c r="K26">
+        <v>170</v>
+      </c>
+      <c r="L26">
+        <v>193.8</v>
+      </c>
+      <c r="M26">
+        <v>85.2783936</v>
+      </c>
+      <c r="N26">
+        <v>108.5216064</v>
+      </c>
+      <c r="O26">
+        <v>26.045185536</v>
+      </c>
+      <c r="P26">
+        <v>82.476420864</v>
+      </c>
+      <c r="Q26">
+        <v>252.476420864</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1148219222407871</v>
+      </c>
+      <c r="T26">
+        <v>0.9522507039796565</v>
+      </c>
+      <c r="U26">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V26">
+        <v>0.24</v>
+      </c>
+      <c r="W26">
+        <v>0.06946400000000001</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>2.272556878932579</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1040955216986612</v>
+      </c>
+      <c r="C27">
+        <v>2687.739298102374</v>
+      </c>
+      <c r="D27">
+        <v>3270.039298102374</v>
+      </c>
+      <c r="E27">
+        <v>-430.6999999999999</v>
+      </c>
+      <c r="F27">
+        <v>971.9</v>
+      </c>
+      <c r="G27">
+        <v>389.6</v>
+      </c>
+      <c r="H27">
+        <v>2485</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>363.8</v>
+      </c>
+      <c r="K27">
+        <v>170</v>
+      </c>
+      <c r="L27">
+        <v>193.8</v>
+      </c>
+      <c r="M27">
+        <v>88.83166000000001</v>
+      </c>
+      <c r="N27">
+        <v>104.96834</v>
+      </c>
+      <c r="O27">
+        <v>25.1924016</v>
+      </c>
+      <c r="P27">
+        <v>79.7759384</v>
+      </c>
+      <c r="Q27">
+        <v>249.7759384</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1156393622648816</v>
+      </c>
+      <c r="T27">
+        <v>0.9624899588611583</v>
+      </c>
+      <c r="U27">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V27">
+        <v>0.24</v>
+      </c>
+      <c r="W27">
+        <v>0.06946400000000001</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>2.181654603775275</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1042550224943242</v>
+      </c>
+      <c r="C28">
+        <v>2643.479488618004</v>
+      </c>
+      <c r="D28">
+        <v>3264.655488618004</v>
+      </c>
+      <c r="E28">
+        <v>-391.8239999999998</v>
+      </c>
+      <c r="F28">
+        <v>1010.776</v>
+      </c>
+      <c r="G28">
+        <v>389.6</v>
+      </c>
+      <c r="H28">
+        <v>2485</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>363.8</v>
+      </c>
+      <c r="K28">
+        <v>170</v>
+      </c>
+      <c r="L28">
+        <v>193.8</v>
+      </c>
+      <c r="M28">
+        <v>92.38492640000001</v>
+      </c>
+      <c r="N28">
+        <v>101.4150736</v>
+      </c>
+      <c r="O28">
+        <v>24.339617664</v>
+      </c>
+      <c r="P28">
+        <v>77.075455936</v>
+      </c>
+      <c r="Q28">
+        <v>247.075455936</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1164788952626003</v>
+      </c>
+      <c r="T28">
+        <v>0.9730059503610788</v>
+      </c>
+      <c r="U28">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V28">
+        <v>0.24</v>
+      </c>
+      <c r="W28">
+        <v>0.06946400000000001</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>2.09774481132238</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1044145232899872</v>
+      </c>
+      <c r="C29">
+        <v>2599.2373778575</v>
+      </c>
+      <c r="D29">
+        <v>3259.2893778575</v>
+      </c>
+      <c r="E29">
+        <v>-352.9479999999999</v>
+      </c>
+      <c r="F29">
+        <v>1049.652</v>
+      </c>
+      <c r="G29">
+        <v>389.6</v>
+      </c>
+      <c r="H29">
+        <v>2485</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>363.8</v>
+      </c>
+      <c r="K29">
+        <v>170</v>
+      </c>
+      <c r="L29">
+        <v>193.8</v>
+      </c>
+      <c r="M29">
+        <v>95.93819280000001</v>
+      </c>
+      <c r="N29">
+        <v>97.8618072</v>
+      </c>
+      <c r="O29">
+        <v>23.486833728</v>
+      </c>
+      <c r="P29">
+        <v>74.37497347199999</v>
+      </c>
+      <c r="Q29">
+        <v>244.374973472</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.117341429164366</v>
+      </c>
+      <c r="T29">
+        <v>0.9838100512171617</v>
+      </c>
+      <c r="U29">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V29">
+        <v>0.24</v>
+      </c>
+      <c r="W29">
+        <v>0.06946400000000001</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>2.020050559051181</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1090641040856502</v>
+      </c>
+      <c r="C30">
+        <v>2411.332646324272</v>
+      </c>
+      <c r="D30">
+        <v>3110.260646324272</v>
+      </c>
+      <c r="E30">
+        <v>-314.0719999999999</v>
+      </c>
+      <c r="F30">
+        <v>1088.528</v>
+      </c>
+      <c r="G30">
+        <v>389.6</v>
+      </c>
+      <c r="H30">
+        <v>2485</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>363.8</v>
+      </c>
+      <c r="K30">
+        <v>170</v>
+      </c>
+      <c r="L30">
+        <v>193.8</v>
+      </c>
+      <c r="M30">
+        <v>122.4594</v>
+      </c>
+      <c r="N30">
+        <v>71.34060000000001</v>
+      </c>
+      <c r="O30">
+        <v>17.121744</v>
+      </c>
+      <c r="P30">
+        <v>54.218856</v>
+      </c>
+      <c r="Q30">
+        <v>224.218856</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1182279223411808</v>
+      </c>
+      <c r="T30">
+        <v>0.9949142659859136</v>
+      </c>
+      <c r="U30">
+        <v>0.1125</v>
+      </c>
+      <c r="V30">
+        <v>0.24</v>
+      </c>
+      <c r="W30">
+        <v>0.08550000000000001</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>1.582565323690954</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1093839648813132</v>
+      </c>
+      <c r="C31">
+        <v>2362.703895248091</v>
+      </c>
+      <c r="D31">
+        <v>3100.507895248091</v>
+      </c>
+      <c r="E31">
+        <v>-275.1959999999999</v>
+      </c>
+      <c r="F31">
+        <v>1127.404</v>
+      </c>
+      <c r="G31">
+        <v>389.6</v>
+      </c>
+      <c r="H31">
+        <v>2485</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>363.8</v>
+      </c>
+      <c r="K31">
+        <v>170</v>
+      </c>
+      <c r="L31">
+        <v>193.8</v>
+      </c>
+      <c r="M31">
+        <v>126.83295</v>
+      </c>
+      <c r="N31">
+        <v>66.96705000000001</v>
+      </c>
+      <c r="O31">
+        <v>16.072092</v>
+      </c>
+      <c r="P31">
+        <v>50.89495800000002</v>
+      </c>
+      <c r="Q31">
+        <v>220.894958</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1191393871567792</v>
+      </c>
+      <c r="T31">
+        <v>1.006331275536884</v>
+      </c>
+      <c r="U31">
+        <v>0.1125</v>
+      </c>
+      <c r="V31">
+        <v>0.24</v>
+      </c>
+      <c r="W31">
+        <v>0.08550000000000001</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>1.527994105632645</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1317528780617195</v>
+      </c>
+      <c r="C32">
+        <v>1766.204633545013</v>
+      </c>
+      <c r="D32">
+        <v>2542.884633545013</v>
+      </c>
+      <c r="E32">
+        <v>-236.3199999999999</v>
+      </c>
+      <c r="F32">
+        <v>1166.28</v>
+      </c>
+      <c r="G32">
+        <v>389.6</v>
+      </c>
+      <c r="H32">
+        <v>2485</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>363.8</v>
+      </c>
+      <c r="K32">
+        <v>170</v>
+      </c>
+      <c r="L32">
+        <v>193.8</v>
+      </c>
+      <c r="M32">
+        <v>229.290648</v>
+      </c>
+      <c r="N32">
+        <v>-35.49064799999999</v>
+      </c>
+      <c r="O32">
+        <v>-8.517755519999998</v>
+      </c>
+      <c r="P32">
+        <v>-26.97289248</v>
+      </c>
+      <c r="Q32">
+        <v>143.02710752</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1210529598697473</v>
+      </c>
+      <c r="T32">
+        <v>1.030300690007471</v>
+      </c>
+      <c r="U32">
+        <v>0.1966</v>
+      </c>
+      <c r="V32">
+        <v>0.2028517098525536</v>
+      </c>
+      <c r="W32">
+        <v>0.156719353842988</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.8452154577189734</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1333308780617195</v>
+      </c>
+      <c r="C33">
+        <v>1695.470418624525</v>
+      </c>
+      <c r="D33">
+        <v>2511.026418624525</v>
+      </c>
+      <c r="E33">
+        <v>-197.444</v>
+      </c>
+      <c r="F33">
+        <v>1205.156</v>
+      </c>
+      <c r="G33">
+        <v>389.6</v>
+      </c>
+      <c r="H33">
+        <v>2485</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>363.8</v>
+      </c>
+      <c r="K33">
+        <v>170</v>
+      </c>
+      <c r="L33">
+        <v>193.8</v>
+      </c>
+      <c r="M33">
+        <v>236.9336696</v>
+      </c>
+      <c r="N33">
+        <v>-43.13366959999996</v>
+      </c>
+      <c r="O33">
+        <v>-10.35208070399999</v>
+      </c>
+      <c r="P33">
+        <v>-32.78158889599997</v>
+      </c>
+      <c r="Q33">
+        <v>137.218411104</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1222450317519176</v>
+      </c>
+      <c r="T33">
+        <v>1.045232584065551</v>
+      </c>
+      <c r="U33">
+        <v>0.1966</v>
+      </c>
+      <c r="V33">
+        <v>0.1963081063089229</v>
+      </c>
+      <c r="W33">
+        <v>0.1580058262996658</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.8179504429538453</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.140713027707417</v>
+      </c>
+      <c r="C34">
+        <v>1517.571636112091</v>
+      </c>
+      <c r="D34">
+        <v>2372.003636112091</v>
+      </c>
+      <c r="E34">
+        <v>-158.568</v>
+      </c>
+      <c r="F34">
+        <v>1244.032</v>
+      </c>
+      <c r="G34">
+        <v>389.6</v>
+      </c>
+      <c r="H34">
+        <v>2485</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>363.8</v>
+      </c>
+      <c r="K34">
+        <v>170</v>
+      </c>
+      <c r="L34">
+        <v>193.8</v>
+      </c>
+      <c r="M34">
+        <v>265.9740416</v>
+      </c>
+      <c r="N34">
+        <v>-72.17404159999995</v>
+      </c>
+      <c r="O34">
+        <v>-17.32176998399999</v>
+      </c>
+      <c r="P34">
+        <v>-54.85227161599997</v>
+      </c>
+      <c r="Q34">
+        <v>115.147728384</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1239135611095892</v>
+      </c>
+      <c r="T34">
+        <v>1.066132585126048</v>
+      </c>
+      <c r="U34">
+        <v>0.2138</v>
+      </c>
+      <c r="V34">
+        <v>0.1748742084761403</v>
+      </c>
+      <c r="W34">
+        <v>0.1764118942278012</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.7286425353172512</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.142463027707417</v>
+      </c>
+      <c r="C35">
+        <v>1447.967066915623</v>
+      </c>
+      <c r="D35">
+        <v>2341.275066915623</v>
+      </c>
+      <c r="E35">
+        <v>-119.6919999999998</v>
+      </c>
+      <c r="F35">
+        <v>1282.908</v>
+      </c>
+      <c r="G35">
+        <v>389.6</v>
+      </c>
+      <c r="H35">
+        <v>2485</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>363.8</v>
+      </c>
+      <c r="K35">
+        <v>170</v>
+      </c>
+      <c r="L35">
+        <v>193.8</v>
+      </c>
+      <c r="M35">
+        <v>274.2857304</v>
+      </c>
+      <c r="N35">
+        <v>-80.48573040000002</v>
+      </c>
+      <c r="O35">
+        <v>-19.316575296</v>
+      </c>
+      <c r="P35">
+        <v>-61.16915510400002</v>
+      </c>
+      <c r="Q35">
+        <v>108.830844896</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1251839127679413</v>
+      </c>
+      <c r="T35">
+        <v>1.082045011769721</v>
+      </c>
+      <c r="U35">
+        <v>0.2138</v>
+      </c>
+      <c r="V35">
+        <v>0.1695749900374693</v>
+      </c>
+      <c r="W35">
+        <v>0.177544867129989</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.7065624584894555</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.144213027707417</v>
+      </c>
+      <c r="C36">
+        <v>1379.148473753252</v>
+      </c>
+      <c r="D36">
+        <v>2311.332473753253</v>
+      </c>
+      <c r="E36">
+        <v>-80.8159999999998</v>
+      </c>
+      <c r="F36">
+        <v>1321.784</v>
+      </c>
+      <c r="G36">
+        <v>389.6</v>
+      </c>
+      <c r="H36">
+        <v>2485</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>363.8</v>
+      </c>
+      <c r="K36">
+        <v>170</v>
+      </c>
+      <c r="L36">
+        <v>193.8</v>
+      </c>
+      <c r="M36">
+        <v>282.5974192</v>
+      </c>
+      <c r="N36">
+        <v>-88.79741919999998</v>
+      </c>
+      <c r="O36">
+        <v>-21.31138060799999</v>
+      </c>
+      <c r="P36">
+        <v>-67.48603859199999</v>
+      </c>
+      <c r="Q36">
+        <v>102.513961408</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1264927599310919</v>
+      </c>
+      <c r="T36">
+        <v>1.098439633160171</v>
+      </c>
+      <c r="U36">
+        <v>0.2138</v>
+      </c>
+      <c r="V36">
+        <v>0.1645874903304849</v>
+      </c>
+      <c r="W36">
+        <v>0.1786111945673423</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.6857812097103539</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.145963027707417</v>
+      </c>
+      <c r="C37">
+        <v>1311.086081845943</v>
+      </c>
+      <c r="D37">
+        <v>2282.146081845944</v>
+      </c>
+      <c r="E37">
+        <v>-41.93999999999983</v>
+      </c>
+      <c r="F37">
+        <v>1360.66</v>
+      </c>
+      <c r="G37">
+        <v>389.6</v>
+      </c>
+      <c r="H37">
+        <v>2485</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>363.8</v>
+      </c>
+      <c r="K37">
+        <v>170</v>
+      </c>
+      <c r="L37">
+        <v>193.8</v>
+      </c>
+      <c r="M37">
+        <v>290.909108</v>
+      </c>
+      <c r="N37">
+        <v>-97.10910799999999</v>
+      </c>
+      <c r="O37">
+        <v>-23.30618592</v>
+      </c>
+      <c r="P37">
+        <v>-73.80292208</v>
+      </c>
+      <c r="Q37">
+        <v>96.19707792</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1278418793146471</v>
+      </c>
+      <c r="T37">
+        <v>1.115338704439558</v>
+      </c>
+      <c r="U37">
+        <v>0.2138</v>
+      </c>
+      <c r="V37">
+        <v>0.1598849906067568</v>
+      </c>
+      <c r="W37">
+        <v>0.1796165890082754</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.6661874608614867</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.147713027707417</v>
+      </c>
+      <c r="C38">
+        <v>1243.75160158683</v>
+      </c>
+      <c r="D38">
+        <v>2253.68760158683</v>
+      </c>
+      <c r="E38">
+        <v>-3.064000000000078</v>
+      </c>
+      <c r="F38">
+        <v>1399.536</v>
+      </c>
+      <c r="G38">
+        <v>389.6</v>
+      </c>
+      <c r="H38">
+        <v>2485</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>363.8</v>
+      </c>
+      <c r="K38">
+        <v>170</v>
+      </c>
+      <c r="L38">
+        <v>193.8</v>
+      </c>
+      <c r="M38">
+        <v>299.2207968</v>
+      </c>
+      <c r="N38">
+        <v>-105.4207967999999</v>
+      </c>
+      <c r="O38">
+        <v>-25.30099123199999</v>
+      </c>
+      <c r="P38">
+        <v>-80.11980556799996</v>
+      </c>
+      <c r="Q38">
+        <v>89.88019443200004</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1292331586789385</v>
+      </c>
+      <c r="T38">
+        <v>1.132765871696426</v>
+      </c>
+      <c r="U38">
+        <v>0.2138</v>
+      </c>
+      <c r="V38">
+        <v>0.1554437408676803</v>
+      </c>
+      <c r="W38">
+        <v>0.1805661282024899</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.6476822536153344</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.149463027707417</v>
+      </c>
+      <c r="C39">
+        <v>1177.118137080857</v>
+      </c>
+      <c r="D39">
+        <v>2225.930137080857</v>
+      </c>
+      <c r="E39">
+        <v>35.81200000000013</v>
+      </c>
+      <c r="F39">
+        <v>1438.412</v>
+      </c>
+      <c r="G39">
+        <v>389.6</v>
+      </c>
+      <c r="H39">
+        <v>2485</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>363.8</v>
+      </c>
+      <c r="K39">
+        <v>170</v>
+      </c>
+      <c r="L39">
+        <v>193.8</v>
+      </c>
+      <c r="M39">
+        <v>307.5324856</v>
+      </c>
+      <c r="N39">
+        <v>-113.7324856</v>
+      </c>
+      <c r="O39">
+        <v>-27.29579654399999</v>
+      </c>
+      <c r="P39">
+        <v>-86.43668905599998</v>
+      </c>
+      <c r="Q39">
+        <v>83.56331094400002</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1306686056420963</v>
+      </c>
+      <c r="T39">
+        <v>1.150746282358274</v>
+      </c>
+      <c r="U39">
+        <v>0.2138</v>
+      </c>
+      <c r="V39">
+        <v>0.1512425586820673</v>
+      </c>
+      <c r="W39">
+        <v>0.181464340953774</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.6301773278419469</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.151213027707417</v>
+      </c>
+      <c r="C40">
+        <v>1111.160101361008</v>
+      </c>
+      <c r="D40">
+        <v>2198.848101361009</v>
+      </c>
+      <c r="E40">
+        <v>74.6880000000001</v>
+      </c>
+      <c r="F40">
+        <v>1477.288</v>
+      </c>
+      <c r="G40">
+        <v>389.6</v>
+      </c>
+      <c r="H40">
+        <v>2485</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>363.8</v>
+      </c>
+      <c r="K40">
+        <v>170</v>
+      </c>
+      <c r="L40">
+        <v>193.8</v>
+      </c>
+      <c r="M40">
+        <v>315.8441744</v>
+      </c>
+      <c r="N40">
+        <v>-122.0441744</v>
+      </c>
+      <c r="O40">
+        <v>-29.29060185599999</v>
+      </c>
+      <c r="P40">
+        <v>-92.75357254399998</v>
+      </c>
+      <c r="Q40">
+        <v>77.24642745600002</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1321503573460011</v>
+      </c>
+      <c r="T40">
+        <v>1.169306706267279</v>
+      </c>
+      <c r="U40">
+        <v>0.2138</v>
+      </c>
+      <c r="V40">
+        <v>0.1472624913483287</v>
+      </c>
+      <c r="W40">
+        <v>0.1823152793497273</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.6135937139513694</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.152963027707417</v>
+      </c>
+      <c r="C41">
+        <v>1045.853137719319</v>
+      </c>
+      <c r="D41">
+        <v>2172.417137719319</v>
+      </c>
+      <c r="E41">
+        <v>113.5640000000001</v>
+      </c>
+      <c r="F41">
+        <v>1516.164</v>
+      </c>
+      <c r="G41">
+        <v>389.6</v>
+      </c>
+      <c r="H41">
+        <v>2485</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>363.8</v>
+      </c>
+      <c r="K41">
+        <v>170</v>
+      </c>
+      <c r="L41">
+        <v>193.8</v>
+      </c>
+      <c r="M41">
+        <v>324.1558632</v>
+      </c>
+      <c r="N41">
+        <v>-130.3558632</v>
+      </c>
+      <c r="O41">
+        <v>-31.285407168</v>
+      </c>
+      <c r="P41">
+        <v>-99.070456032</v>
+      </c>
+      <c r="Q41">
+        <v>70.929543968</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1336806910729847</v>
+      </c>
+      <c r="T41">
+        <v>1.188475668665103</v>
+      </c>
+      <c r="U41">
+        <v>0.2138</v>
+      </c>
+      <c r="V41">
+        <v>0.1434865300317048</v>
+      </c>
+      <c r="W41">
+        <v>0.1831225798792215</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.5978605417987701</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.154713027707417</v>
+      </c>
+      <c r="C42">
+        <v>981.1740466442807</v>
+      </c>
+      <c r="D42">
+        <v>2146.614046644281</v>
+      </c>
+      <c r="E42">
+        <v>152.4400000000001</v>
+      </c>
+      <c r="F42">
+        <v>1555.04</v>
+      </c>
+      <c r="G42">
+        <v>389.6</v>
+      </c>
+      <c r="H42">
+        <v>2485</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>363.8</v>
+      </c>
+      <c r="K42">
+        <v>170</v>
+      </c>
+      <c r="L42">
+        <v>193.8</v>
+      </c>
+      <c r="M42">
+        <v>332.467552</v>
+      </c>
+      <c r="N42">
+        <v>-138.6675519999999</v>
+      </c>
+      <c r="O42">
+        <v>-33.28021247999999</v>
+      </c>
+      <c r="P42">
+        <v>-105.38733952</v>
+      </c>
+      <c r="Q42">
+        <v>64.61266048000005</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1352620359242011</v>
+      </c>
+      <c r="T42">
+        <v>1.208283596476188</v>
+      </c>
+      <c r="U42">
+        <v>0.2138</v>
+      </c>
+      <c r="V42">
+        <v>0.1398993667809122</v>
+      </c>
+      <c r="W42">
+        <v>0.183889515382241</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.582914028253801</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.156463027707417</v>
+      </c>
+      <c r="C43">
+        <v>917.1007179039748</v>
+      </c>
+      <c r="D43">
+        <v>2121.416717903975</v>
+      </c>
+      <c r="E43">
+        <v>191.3160000000003</v>
+      </c>
+      <c r="F43">
+        <v>1593.916</v>
+      </c>
+      <c r="G43">
+        <v>389.6</v>
+      </c>
+      <c r="H43">
+        <v>2485</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>363.8</v>
+      </c>
+      <c r="K43">
+        <v>170</v>
+      </c>
+      <c r="L43">
+        <v>193.8</v>
+      </c>
+      <c r="M43">
+        <v>340.7792408</v>
+      </c>
+      <c r="N43">
+        <v>-146.9792408</v>
+      </c>
+      <c r="O43">
+        <v>-35.275017792</v>
+      </c>
+      <c r="P43">
+        <v>-111.704223008</v>
+      </c>
+      <c r="Q43">
+        <v>58.29577699199999</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1368969856856282</v>
+      </c>
+      <c r="T43">
+        <v>1.22876297946731</v>
+      </c>
+      <c r="U43">
+        <v>0.2138</v>
+      </c>
+      <c r="V43">
+        <v>0.136487187103329</v>
+      </c>
+      <c r="W43">
+        <v>0.1846190393973083</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.5686966129305374</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.158213027707417</v>
+      </c>
+      <c r="C44">
+        <v>853.6120673570372</v>
+      </c>
+      <c r="D44">
+        <v>2096.804067357037</v>
+      </c>
+      <c r="E44">
+        <v>230.192</v>
+      </c>
+      <c r="F44">
+        <v>1632.792</v>
+      </c>
+      <c r="G44">
+        <v>389.6</v>
+      </c>
+      <c r="H44">
+        <v>2485</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>363.8</v>
+      </c>
+      <c r="K44">
+        <v>170</v>
+      </c>
+      <c r="L44">
+        <v>193.8</v>
+      </c>
+      <c r="M44">
+        <v>349.0909296</v>
+      </c>
+      <c r="N44">
+        <v>-155.2909296</v>
+      </c>
+      <c r="O44">
+        <v>-37.26982310399999</v>
+      </c>
+      <c r="P44">
+        <v>-118.021106496</v>
+      </c>
+      <c r="Q44">
+        <v>51.97889350400001</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1385883130250356</v>
+      </c>
+      <c r="T44">
+        <v>1.249948548078815</v>
+      </c>
+      <c r="U44">
+        <v>0.2138</v>
+      </c>
+      <c r="V44">
+        <v>0.1332374921722974</v>
+      </c>
+      <c r="W44">
+        <v>0.1853138241735628</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.5551562173845723</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.159963027707417</v>
+      </c>
+      <c r="C45">
+        <v>790.6879781118698</v>
+      </c>
+      <c r="D45">
+        <v>2072.75597811187</v>
+      </c>
+      <c r="E45">
+        <v>269.068</v>
+      </c>
+      <c r="F45">
+        <v>1671.668</v>
+      </c>
+      <c r="G45">
+        <v>389.6</v>
+      </c>
+      <c r="H45">
+        <v>2485</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>363.8</v>
+      </c>
+      <c r="K45">
+        <v>170</v>
+      </c>
+      <c r="L45">
+        <v>193.8</v>
+      </c>
+      <c r="M45">
+        <v>357.4026183999999</v>
+      </c>
+      <c r="N45">
+        <v>-163.6026183999999</v>
+      </c>
+      <c r="O45">
+        <v>-39.26462841599998</v>
+      </c>
+      <c r="P45">
+        <v>-124.3379899839999</v>
+      </c>
+      <c r="Q45">
+        <v>45.66201001600005</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1403389851833695</v>
+      </c>
+      <c r="T45">
+        <v>1.271877469974934</v>
+      </c>
+      <c r="U45">
+        <v>0.2138</v>
+      </c>
+      <c r="V45">
+        <v>0.130138945842709</v>
+      </c>
+      <c r="W45">
+        <v>0.1859762933788288</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.5422456076779544</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.161713027707417</v>
+      </c>
+      <c r="C46">
+        <v>728.3092456890004</v>
+      </c>
+      <c r="D46">
+        <v>2049.253245689</v>
+      </c>
+      <c r="E46">
+        <v>307.944</v>
+      </c>
+      <c r="F46">
+        <v>1710.544</v>
+      </c>
+      <c r="G46">
+        <v>389.6</v>
+      </c>
+      <c r="H46">
+        <v>2485</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>363.8</v>
+      </c>
+      <c r="K46">
+        <v>170</v>
+      </c>
+      <c r="L46">
+        <v>193.8</v>
+      </c>
+      <c r="M46">
+        <v>365.7143072</v>
+      </c>
+      <c r="N46">
+        <v>-171.9143071999999</v>
+      </c>
+      <c r="O46">
+        <v>-41.25943372799998</v>
+      </c>
+      <c r="P46">
+        <v>-130.654873472</v>
+      </c>
+      <c r="Q46">
+        <v>39.34512652800004</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1421521813473583</v>
+      </c>
+      <c r="T46">
+        <v>1.294589567653059</v>
+      </c>
+      <c r="U46">
+        <v>0.2138</v>
+      </c>
+      <c r="V46">
+        <v>0.127181242528102</v>
+      </c>
+      <c r="W46">
+        <v>0.1866086503474918</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.5299218438670918</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1634630277074171</v>
+      </c>
+      <c r="C47">
+        <v>666.4575268723852</v>
+      </c>
+      <c r="D47">
+        <v>2026.277526872385</v>
+      </c>
+      <c r="E47">
+        <v>346.8200000000002</v>
+      </c>
+      <c r="F47">
+        <v>1749.42</v>
+      </c>
+      <c r="G47">
+        <v>389.6</v>
+      </c>
+      <c r="H47">
+        <v>2485</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>363.8</v>
+      </c>
+      <c r="K47">
+        <v>170</v>
+      </c>
+      <c r="L47">
+        <v>193.8</v>
+      </c>
+      <c r="M47">
+        <v>374.025996</v>
+      </c>
+      <c r="N47">
+        <v>-180.225996</v>
+      </c>
+      <c r="O47">
+        <v>-43.25423904</v>
+      </c>
+      <c r="P47">
+        <v>-136.97175696</v>
+      </c>
+      <c r="Q47">
+        <v>33.02824304000001</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1440313119173103</v>
+      </c>
+      <c r="T47">
+        <v>1.318127559792205</v>
+      </c>
+      <c r="U47">
+        <v>0.2138</v>
+      </c>
+      <c r="V47">
+        <v>0.1243549926941442</v>
+      </c>
+      <c r="W47">
+        <v>0.187212902561992</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.5181458028922674</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.165213027707417</v>
+      </c>
+      <c r="C48">
+        <v>605.1152919633716</v>
+      </c>
+      <c r="D48">
+        <v>2003.811291963372</v>
+      </c>
+      <c r="E48">
+        <v>385.6960000000001</v>
+      </c>
+      <c r="F48">
+        <v>1788.296</v>
+      </c>
+      <c r="G48">
+        <v>389.6</v>
+      </c>
+      <c r="H48">
+        <v>2485</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>363.8</v>
+      </c>
+      <c r="K48">
+        <v>170</v>
+      </c>
+      <c r="L48">
+        <v>193.8</v>
+      </c>
+      <c r="M48">
+        <v>382.3376848</v>
+      </c>
+      <c r="N48">
+        <v>-188.5376848</v>
+      </c>
+      <c r="O48">
+        <v>-45.24904435199999</v>
+      </c>
+      <c r="P48">
+        <v>-143.288640448</v>
+      </c>
+      <c r="Q48">
+        <v>26.71135955200003</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.145980039915779</v>
+      </c>
+      <c r="T48">
+        <v>1.342537329417987</v>
+      </c>
+      <c r="U48">
+        <v>0.2138</v>
+      </c>
+      <c r="V48">
+        <v>0.1216516232877498</v>
+      </c>
+      <c r="W48">
+        <v>0.1877908829410791</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.5068817636989573</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1790721964943272</v>
+      </c>
+      <c r="C49">
+        <v>404.4926163017681</v>
+      </c>
+      <c r="D49">
+        <v>1842.064616301768</v>
+      </c>
+      <c r="E49">
+        <v>424.5720000000001</v>
+      </c>
+      <c r="F49">
+        <v>1827.172</v>
+      </c>
+      <c r="G49">
+        <v>389.6</v>
+      </c>
+      <c r="H49">
+        <v>2485</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>363.8</v>
+      </c>
+      <c r="K49">
+        <v>170</v>
+      </c>
+      <c r="L49">
+        <v>193.8</v>
+      </c>
+      <c r="M49">
+        <v>436.3286736</v>
+      </c>
+      <c r="N49">
+        <v>-242.5286736</v>
+      </c>
+      <c r="O49">
+        <v>-58.20688166399999</v>
+      </c>
+      <c r="P49">
+        <v>-184.321791936</v>
+      </c>
+      <c r="Q49">
+        <v>-14.32179193600001</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1486799817762845</v>
+      </c>
+      <c r="T49">
+        <v>1.376356804927002</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.1065985409949001</v>
+      </c>
+      <c r="W49">
+        <v>0.2133442684104178</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.4441605874787505</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1810721964943272</v>
+      </c>
+      <c r="C50">
+        <v>344.4063286467745</v>
+      </c>
+      <c r="D50">
+        <v>1820.854328646774</v>
+      </c>
+      <c r="E50">
+        <v>463.4479999999999</v>
+      </c>
+      <c r="F50">
+        <v>1866.048</v>
+      </c>
+      <c r="G50">
+        <v>389.6</v>
+      </c>
+      <c r="H50">
+        <v>2485</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>363.8</v>
+      </c>
+      <c r="K50">
+        <v>170</v>
+      </c>
+      <c r="L50">
+        <v>193.8</v>
+      </c>
+      <c r="M50">
+        <v>445.6122624</v>
+      </c>
+      <c r="N50">
+        <v>-251.8122624</v>
+      </c>
+      <c r="O50">
+        <v>-60.43494297599999</v>
+      </c>
+      <c r="P50">
+        <v>-191.3773194239999</v>
+      </c>
+      <c r="Q50">
+        <v>-21.37731942399995</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1507930583489054</v>
+      </c>
+      <c r="T50">
+        <v>1.402825205021752</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.1043777380575064</v>
+      </c>
+      <c r="W50">
+        <v>0.2138745961518675</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.4349072419062766</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1830721964943272</v>
+      </c>
+      <c r="C51">
+        <v>284.8029287304103</v>
+      </c>
+      <c r="D51">
+        <v>1800.12692873041</v>
+      </c>
+      <c r="E51">
+        <v>502.3240000000001</v>
+      </c>
+      <c r="F51">
+        <v>1904.924</v>
+      </c>
+      <c r="G51">
+        <v>389.6</v>
+      </c>
+      <c r="H51">
+        <v>2485</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>363.8</v>
+      </c>
+      <c r="K51">
+        <v>170</v>
+      </c>
+      <c r="L51">
+        <v>193.8</v>
+      </c>
+      <c r="M51">
+        <v>454.8958512</v>
+      </c>
+      <c r="N51">
+        <v>-261.0958512</v>
+      </c>
+      <c r="O51">
+        <v>-62.663004288</v>
+      </c>
+      <c r="P51">
+        <v>-198.432846912</v>
+      </c>
+      <c r="Q51">
+        <v>-28.43284691200003</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1529890006694722</v>
+      </c>
+      <c r="T51">
+        <v>1.430331581590806</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.1022475801379654</v>
+      </c>
+      <c r="W51">
+        <v>0.2143832778630539</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.4260315839081893</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1850721964943272</v>
+      </c>
+      <c r="C52">
+        <v>225.6661115354411</v>
+      </c>
+      <c r="D52">
+        <v>1779.866111535441</v>
+      </c>
+      <c r="E52">
+        <v>541.2</v>
+      </c>
+      <c r="F52">
+        <v>1943.8</v>
+      </c>
+      <c r="G52">
+        <v>389.6</v>
+      </c>
+      <c r="H52">
+        <v>2485</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>363.8</v>
+      </c>
+      <c r="K52">
+        <v>170</v>
+      </c>
+      <c r="L52">
+        <v>193.8</v>
+      </c>
+      <c r="M52">
+        <v>464.17944</v>
+      </c>
+      <c r="N52">
+        <v>-270.37944</v>
+      </c>
+      <c r="O52">
+        <v>-64.89106559999999</v>
+      </c>
+      <c r="P52">
+        <v>-205.4883744</v>
+      </c>
+      <c r="Q52">
+        <v>-35.4883744</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1552727806828616</v>
+      </c>
+      <c r="T52">
+        <v>1.458938213222622</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.1002026285352061</v>
+      </c>
+      <c r="W52">
+        <v>0.2148716123057928</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.4175109522300255</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1870721964943272</v>
+      </c>
+      <c r="C53">
+        <v>166.9802979404767</v>
+      </c>
+      <c r="D53">
+        <v>1760.056297940477</v>
+      </c>
+      <c r="E53">
+        <v>580.076</v>
+      </c>
+      <c r="F53">
+        <v>1982.676</v>
+      </c>
+      <c r="G53">
+        <v>389.6</v>
+      </c>
+      <c r="H53">
+        <v>2485</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>363.8</v>
+      </c>
+      <c r="K53">
+        <v>170</v>
+      </c>
+      <c r="L53">
+        <v>193.8</v>
+      </c>
+      <c r="M53">
+        <v>473.4630288</v>
+      </c>
+      <c r="N53">
+        <v>-279.6630288</v>
+      </c>
+      <c r="O53">
+        <v>-67.119126912</v>
+      </c>
+      <c r="P53">
+        <v>-212.543901888</v>
+      </c>
+      <c r="Q53">
+        <v>-42.54390188799999</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1576497762070016</v>
+      </c>
+      <c r="T53">
+        <v>1.488712462472063</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.09823787111294718</v>
+      </c>
+      <c r="W53">
+        <v>0.2153407963782282</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.4093244629706133</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1890721964943272</v>
+      </c>
+      <c r="C54">
+        <v>108.7305947687141</v>
+      </c>
+      <c r="D54">
+        <v>1740.682594768714</v>
+      </c>
+      <c r="E54">
+        <v>618.9520000000002</v>
+      </c>
+      <c r="F54">
+        <v>2021.552</v>
+      </c>
+      <c r="G54">
+        <v>389.6</v>
+      </c>
+      <c r="H54">
+        <v>2485</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>363.8</v>
+      </c>
+      <c r="K54">
+        <v>170</v>
+      </c>
+      <c r="L54">
+        <v>193.8</v>
+      </c>
+      <c r="M54">
+        <v>482.7466176</v>
+      </c>
+      <c r="N54">
+        <v>-288.9466176</v>
+      </c>
+      <c r="O54">
+        <v>-69.34718822400001</v>
+      </c>
+      <c r="P54">
+        <v>-219.599429376</v>
+      </c>
+      <c r="Q54">
+        <v>-49.59942937600002</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1601258132113141</v>
+      </c>
+      <c r="T54">
+        <v>1.519727305440231</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.09634868128385204</v>
+      </c>
+      <c r="W54">
+        <v>0.2157919349094161</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.4014528386827169</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1910721964943272</v>
+      </c>
+      <c r="C55">
+        <v>50.90275744652399</v>
+      </c>
+      <c r="D55">
+        <v>1721.730757446524</v>
+      </c>
+      <c r="E55">
+        <v>657.828</v>
+      </c>
+      <c r="F55">
+        <v>2060.428</v>
+      </c>
+      <c r="G55">
+        <v>389.6</v>
+      </c>
+      <c r="H55">
+        <v>2485</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>363.8</v>
+      </c>
+      <c r="K55">
+        <v>170</v>
+      </c>
+      <c r="L55">
+        <v>193.8</v>
+      </c>
+      <c r="M55">
+        <v>492.0302064</v>
+      </c>
+      <c r="N55">
+        <v>-298.2302064</v>
+      </c>
+      <c r="O55">
+        <v>-71.57524953599999</v>
+      </c>
+      <c r="P55">
+        <v>-226.654956864</v>
+      </c>
+      <c r="Q55">
+        <v>-56.65495686399998</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.162707213492406</v>
+      </c>
+      <c r="T55">
+        <v>1.552061928960236</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.09453078163698692</v>
+      </c>
+      <c r="W55">
+        <v>0.2162260493450875</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.3938782568207788</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1930721964943272</v>
+      </c>
+      <c r="C56">
+        <v>-6.516844924886755</v>
+      </c>
+      <c r="D56">
+        <v>1703.187155075113</v>
+      </c>
+      <c r="E56">
+        <v>696.7040000000002</v>
+      </c>
+      <c r="F56">
+        <v>2099.304</v>
+      </c>
+      <c r="G56">
+        <v>389.6</v>
+      </c>
+      <c r="H56">
+        <v>2485</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>363.8</v>
+      </c>
+      <c r="K56">
+        <v>170</v>
+      </c>
+      <c r="L56">
+        <v>193.8</v>
+      </c>
+      <c r="M56">
+        <v>501.3137952000001</v>
+      </c>
+      <c r="N56">
+        <v>-307.5137952000001</v>
+      </c>
+      <c r="O56">
+        <v>-73.80331084800001</v>
+      </c>
+      <c r="P56">
+        <v>-233.710484352</v>
+      </c>
+      <c r="Q56">
+        <v>-63.71048435200004</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1654008485683278</v>
+      </c>
+      <c r="T56">
+        <v>1.585802405676763</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.09278021160667232</v>
+      </c>
+      <c r="W56">
+        <v>0.2166440854683267</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.3865842150278014</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1950721964943272</v>
+      </c>
+      <c r="C57">
+        <v>-63.54126226473181</v>
+      </c>
+      <c r="D57">
+        <v>1685.038737735268</v>
+      </c>
+      <c r="E57">
+        <v>735.5800000000004</v>
+      </c>
+      <c r="F57">
+        <v>2138.18</v>
+      </c>
+      <c r="G57">
+        <v>389.6</v>
+      </c>
+      <c r="H57">
+        <v>2485</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>363.8</v>
+      </c>
+      <c r="K57">
+        <v>170</v>
+      </c>
+      <c r="L57">
+        <v>193.8</v>
+      </c>
+      <c r="M57">
+        <v>510.5973840000001</v>
+      </c>
+      <c r="N57">
+        <v>-316.7973840000001</v>
+      </c>
+      <c r="O57">
+        <v>-76.03137216000002</v>
+      </c>
+      <c r="P57">
+        <v>-240.7660118400001</v>
+      </c>
+      <c r="Q57">
+        <v>-70.76601184000006</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1682142007587351</v>
+      </c>
+      <c r="T57">
+        <v>1.621042459136247</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.09109329866836918</v>
+      </c>
+      <c r="W57">
+        <v>0.2170469202779934</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.379555411118205</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1970721964943272</v>
+      </c>
+      <c r="C58">
+        <v>-120.1829941396159</v>
+      </c>
+      <c r="D58">
+        <v>1667.273005860384</v>
+      </c>
+      <c r="E58">
+        <v>774.4560000000001</v>
+      </c>
+      <c r="F58">
+        <v>2177.056</v>
+      </c>
+      <c r="G58">
+        <v>389.6</v>
+      </c>
+      <c r="H58">
+        <v>2485</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>363.8</v>
+      </c>
+      <c r="K58">
+        <v>170</v>
+      </c>
+      <c r="L58">
+        <v>193.8</v>
+      </c>
+      <c r="M58">
+        <v>519.8809728</v>
+      </c>
+      <c r="N58">
+        <v>-326.0809728</v>
+      </c>
+      <c r="O58">
+        <v>-78.259433472</v>
+      </c>
+      <c r="P58">
+        <v>-247.821539328</v>
+      </c>
+      <c r="Q58">
+        <v>-77.82153932799997</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1711554325941609</v>
+      </c>
+      <c r="T58">
+        <v>1.657884333207525</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.08946663262071976</v>
+      </c>
+      <c r="W58">
+        <v>0.2174353681301721</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.3727776359196657</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1990721964943272</v>
+      </c>
+      <c r="C59">
+        <v>-176.454018473285</v>
+      </c>
+      <c r="D59">
+        <v>1649.877981526715</v>
+      </c>
+      <c r="E59">
+        <v>813.3320000000003</v>
+      </c>
+      <c r="F59">
+        <v>2215.932</v>
+      </c>
+      <c r="G59">
+        <v>389.6</v>
+      </c>
+      <c r="H59">
+        <v>2485</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>363.8</v>
+      </c>
+      <c r="K59">
+        <v>170</v>
+      </c>
+      <c r="L59">
+        <v>193.8</v>
+      </c>
+      <c r="M59">
+        <v>529.1645616000001</v>
+      </c>
+      <c r="N59">
+        <v>-335.3645616000001</v>
+      </c>
+      <c r="O59">
+        <v>-80.48749478400001</v>
+      </c>
+      <c r="P59">
+        <v>-254.8770668160001</v>
+      </c>
+      <c r="Q59">
+        <v>-84.87706681600005</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1742334659103042</v>
+      </c>
+      <c r="T59">
+        <v>1.696439782817002</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.08789704257474221</v>
+      </c>
+      <c r="W59">
+        <v>0.2178101862331516</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.3662376773947592</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2010721964943272</v>
+      </c>
+      <c r="C60">
+        <v>-232.3658184777137</v>
+      </c>
+      <c r="D60">
+        <v>1632.842181522286</v>
+      </c>
+      <c r="E60">
+        <v>852.2080000000001</v>
+      </c>
+      <c r="F60">
+        <v>2254.808</v>
+      </c>
+      <c r="G60">
+        <v>389.6</v>
+      </c>
+      <c r="H60">
+        <v>2485</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>363.8</v>
+      </c>
+      <c r="K60">
+        <v>170</v>
+      </c>
+      <c r="L60">
+        <v>193.8</v>
+      </c>
+      <c r="M60">
+        <v>538.4481504</v>
+      </c>
+      <c r="N60">
+        <v>-344.6481504</v>
+      </c>
+      <c r="O60">
+        <v>-82.715556096</v>
+      </c>
+      <c r="P60">
+        <v>-261.932594304</v>
+      </c>
+      <c r="Q60">
+        <v>-91.93259430400002</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1774580722415019</v>
+      </c>
+      <c r="T60">
+        <v>1.736831206217407</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.08638157632345354</v>
+      </c>
+      <c r="W60">
+        <v>0.2181720795739593</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.3599232346810565</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2030721964943272</v>
+      </c>
+      <c r="C61">
+        <v>-287.9294079327956</v>
+      </c>
+      <c r="D61">
+        <v>1616.154592067204</v>
+      </c>
+      <c r="E61">
+        <v>891.0839999999998</v>
+      </c>
+      <c r="F61">
+        <v>2293.684</v>
+      </c>
+      <c r="G61">
+        <v>389.6</v>
+      </c>
+      <c r="H61">
+        <v>2485</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>363.8</v>
+      </c>
+      <c r="K61">
+        <v>170</v>
+      </c>
+      <c r="L61">
+        <v>193.8</v>
+      </c>
+      <c r="M61">
+        <v>547.7317392</v>
+      </c>
+      <c r="N61">
+        <v>-353.9317392</v>
+      </c>
+      <c r="O61">
+        <v>-84.94361740799999</v>
+      </c>
+      <c r="P61">
+        <v>-268.988121792</v>
+      </c>
+      <c r="Q61">
+        <v>-98.98812179200002</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1808399764425141</v>
+      </c>
+      <c r="T61">
+        <v>1.779192942954417</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.08491748180949672</v>
+      </c>
+      <c r="W61">
+        <v>0.2185217053438922</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.3538228408729031</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2050721964943272</v>
+      </c>
+      <c r="C62">
+        <v>-343.155354931559</v>
+      </c>
+      <c r="D62">
+        <v>1599.804645068441</v>
+      </c>
+      <c r="E62">
+        <v>929.96</v>
+      </c>
+      <c r="F62">
+        <v>2332.56</v>
+      </c>
+      <c r="G62">
+        <v>389.6</v>
+      </c>
+      <c r="H62">
+        <v>2485</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>363.8</v>
+      </c>
+      <c r="K62">
+        <v>170</v>
+      </c>
+      <c r="L62">
+        <v>193.8</v>
+      </c>
+      <c r="M62">
+        <v>557.0153280000001</v>
+      </c>
+      <c r="N62">
+        <v>-363.2153280000001</v>
+      </c>
+      <c r="O62">
+        <v>-87.17167872000002</v>
+      </c>
+      <c r="P62">
+        <v>-276.0436492800001</v>
+      </c>
+      <c r="Q62">
+        <v>-106.0436492800001</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.184390975853577</v>
+      </c>
+      <c r="T62">
+        <v>1.823672766528277</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.0835021904460051</v>
+      </c>
+      <c r="W62">
+        <v>0.218859676921494</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.3479257935250213</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2070721964943272</v>
+      </c>
+      <c r="C63">
+        <v>-398.0538041985055</v>
+      </c>
+      <c r="D63">
+        <v>1583.782195801494</v>
+      </c>
+      <c r="E63">
+        <v>968.8359999999998</v>
+      </c>
+      <c r="F63">
+        <v>2371.436</v>
+      </c>
+      <c r="G63">
+        <v>389.6</v>
+      </c>
+      <c r="H63">
+        <v>2485</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>363.8</v>
+      </c>
+      <c r="K63">
+        <v>170</v>
+      </c>
+      <c r="L63">
+        <v>193.8</v>
+      </c>
+      <c r="M63">
+        <v>566.2989167999999</v>
+      </c>
+      <c r="N63">
+        <v>-372.4989167999999</v>
+      </c>
+      <c r="O63">
+        <v>-89.39974003199997</v>
+      </c>
+      <c r="P63">
+        <v>-283.0991767679999</v>
+      </c>
+      <c r="Q63">
+        <v>-113.0991767679999</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1881240777985405</v>
+      </c>
+      <c r="T63">
+        <v>1.870433606695669</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.08213330207803783</v>
+      </c>
+      <c r="W63">
+        <v>0.2191865674637646</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.3422220919918243</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2090721964943272</v>
+      </c>
+      <c r="C64">
+        <v>-452.6344980800995</v>
+      </c>
+      <c r="D64">
+        <v>1568.0775019199</v>
+      </c>
+      <c r="E64">
+        <v>1007.712</v>
+      </c>
+      <c r="F64">
+        <v>2410.312</v>
+      </c>
+      <c r="G64">
+        <v>389.6</v>
+      </c>
+      <c r="H64">
+        <v>2485</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>363.8</v>
+      </c>
+      <c r="K64">
+        <v>170</v>
+      </c>
+      <c r="L64">
+        <v>193.8</v>
+      </c>
+      <c r="M64">
+        <v>575.5825056</v>
+      </c>
+      <c r="N64">
+        <v>-381.7825056</v>
+      </c>
+      <c r="O64">
+        <v>-91.62780134399999</v>
+      </c>
+      <c r="P64">
+        <v>-290.154704256</v>
+      </c>
+      <c r="Q64">
+        <v>-120.154704256</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1920536587932389</v>
+      </c>
+      <c r="T64">
+        <v>1.919655543713976</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.08080857139935979</v>
+      </c>
+      <c r="W64">
+        <v>0.2195029131498329</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.3367023808306657</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2110721964943272</v>
+      </c>
+      <c r="C65">
+        <v>-506.9067962986778</v>
+      </c>
+      <c r="D65">
+        <v>1552.681203701322</v>
+      </c>
+      <c r="E65">
+        <v>1046.588</v>
+      </c>
+      <c r="F65">
+        <v>2449.188</v>
+      </c>
+      <c r="G65">
+        <v>389.6</v>
+      </c>
+      <c r="H65">
+        <v>2485</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>363.8</v>
+      </c>
+      <c r="K65">
+        <v>170</v>
+      </c>
+      <c r="L65">
+        <v>193.8</v>
+      </c>
+      <c r="M65">
+        <v>584.8660944000001</v>
+      </c>
+      <c r="N65">
+        <v>-391.0660944000001</v>
+      </c>
+      <c r="O65">
+        <v>-93.85586265600001</v>
+      </c>
+      <c r="P65">
+        <v>-297.2102317440001</v>
+      </c>
+      <c r="Q65">
+        <v>-127.2102317440001</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1961956495714346</v>
+      </c>
+      <c r="T65">
+        <v>1.971538125976516</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.079525895662862</v>
+      </c>
+      <c r="W65">
+        <v>0.2198092161157086</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.3313578985952583</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2130721964943272</v>
+      </c>
+      <c r="C66">
+        <v>-560.8796945539416</v>
+      </c>
+      <c r="D66">
+        <v>1537.584305446058</v>
+      </c>
+      <c r="E66">
+        <v>1085.464</v>
+      </c>
+      <c r="F66">
+        <v>2488.064</v>
+      </c>
+      <c r="G66">
+        <v>389.6</v>
+      </c>
+      <c r="H66">
+        <v>2485</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>363.8</v>
+      </c>
+      <c r="K66">
+        <v>170</v>
+      </c>
+      <c r="L66">
+        <v>193.8</v>
+      </c>
+      <c r="M66">
+        <v>594.1496832</v>
+      </c>
+      <c r="N66">
+        <v>-400.3496832</v>
+      </c>
+      <c r="O66">
+        <v>-96.08392396799999</v>
+      </c>
+      <c r="P66">
+        <v>-304.2657592320001</v>
+      </c>
+      <c r="Q66">
+        <v>-134.2657592320001</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2005677509484189</v>
+      </c>
+      <c r="T66">
+        <v>2.026303073920308</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.07828330354312978</v>
+      </c>
+      <c r="W66">
+        <v>0.2201059471139006</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.3261804314297074</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2150721964943272</v>
+      </c>
+      <c r="C67">
+        <v>-614.5618420497131</v>
+      </c>
+      <c r="D67">
+        <v>1522.778157950287</v>
+      </c>
+      <c r="E67">
+        <v>1124.34</v>
+      </c>
+      <c r="F67">
+        <v>2526.94</v>
+      </c>
+      <c r="G67">
+        <v>389.6</v>
+      </c>
+      <c r="H67">
+        <v>2485</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>363.8</v>
+      </c>
+      <c r="K67">
+        <v>170</v>
+      </c>
+      <c r="L67">
+        <v>193.8</v>
+      </c>
+      <c r="M67">
+        <v>603.433272</v>
+      </c>
+      <c r="N67">
+        <v>-409.633272</v>
+      </c>
+      <c r="O67">
+        <v>-98.31198527999999</v>
+      </c>
+      <c r="P67">
+        <v>-311.32128672</v>
+      </c>
+      <c r="Q67">
+        <v>-141.32128672</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2051896866898023</v>
+      </c>
+      <c r="T67">
+        <v>2.084197447460888</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.07707894502708164</v>
+      </c>
+      <c r="W67">
+        <v>0.2203935479275329</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.3211622709461736</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2170721964943272</v>
+      </c>
+      <c r="C68">
+        <v>-667.961558017706</v>
+      </c>
+      <c r="D68">
+        <v>1508.254441982294</v>
+      </c>
+      <c r="E68">
+        <v>1163.216</v>
+      </c>
+      <c r="F68">
+        <v>2565.816</v>
+      </c>
+      <c r="G68">
+        <v>389.6</v>
+      </c>
+      <c r="H68">
+        <v>2485</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>363.8</v>
+      </c>
+      <c r="K68">
+        <v>170</v>
+      </c>
+      <c r="L68">
+        <v>193.8</v>
+      </c>
+      <c r="M68">
+        <v>612.7168608000001</v>
+      </c>
+      <c r="N68">
+        <v>-418.9168608000001</v>
+      </c>
+      <c r="O68">
+        <v>-100.540046592</v>
+      </c>
+      <c r="P68">
+        <v>-318.376814208</v>
+      </c>
+      <c r="Q68">
+        <v>-148.376814208</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2100835010042083</v>
+      </c>
+      <c r="T68">
+        <v>2.145497372386209</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.075911082223641</v>
+      </c>
+      <c r="W68">
+        <v>0.2206724335649946</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.3162961759318375</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2190721964943272</v>
+      </c>
+      <c r="C69">
+        <v>-721.0868473046444</v>
+      </c>
+      <c r="D69">
+        <v>1494.005152695356</v>
+      </c>
+      <c r="E69">
+        <v>1202.092</v>
+      </c>
+      <c r="F69">
+        <v>2604.692</v>
+      </c>
+      <c r="G69">
+        <v>389.6</v>
+      </c>
+      <c r="H69">
+        <v>2485</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>363.8</v>
+      </c>
+      <c r="K69">
+        <v>170</v>
+      </c>
+      <c r="L69">
+        <v>193.8</v>
+      </c>
+      <c r="M69">
+        <v>622.0004496</v>
+      </c>
+      <c r="N69">
+        <v>-428.2004496</v>
+      </c>
+      <c r="O69">
+        <v>-102.768107904</v>
+      </c>
+      <c r="P69">
+        <v>-325.432341696</v>
+      </c>
+      <c r="Q69">
+        <v>-155.432341696</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2152739101255479</v>
+      </c>
+      <c r="T69">
+        <v>2.2105124442767</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.07477808099642248</v>
+      </c>
+      <c r="W69">
+        <v>0.2209429942580543</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.3115753374850937</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2210721964943272</v>
+      </c>
+      <c r="C70">
+        <v>-773.9454150840911</v>
+      </c>
+      <c r="D70">
+        <v>1480.022584915909</v>
+      </c>
+      <c r="E70">
+        <v>1240.968</v>
+      </c>
+      <c r="F70">
+        <v>2643.568</v>
+      </c>
+      <c r="G70">
+        <v>389.6</v>
+      </c>
+      <c r="H70">
+        <v>2485</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>363.8</v>
+      </c>
+      <c r="K70">
+        <v>170</v>
+      </c>
+      <c r="L70">
+        <v>193.8</v>
+      </c>
+      <c r="M70">
+        <v>631.2840384000001</v>
+      </c>
+      <c r="N70">
+        <v>-437.4840384000001</v>
+      </c>
+      <c r="O70">
+        <v>-104.996169216</v>
+      </c>
+      <c r="P70">
+        <v>-332.4878691840001</v>
+      </c>
+      <c r="Q70">
+        <v>-162.4878691840001</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2207887198169713</v>
+      </c>
+      <c r="T70">
+        <v>2.279590958160347</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.07367840333471037</v>
+      </c>
+      <c r="W70">
+        <v>0.2212055972836712</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.3069933472279599</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2230721964943272</v>
+      </c>
+      <c r="C71">
+        <v>-826.5446807497974</v>
+      </c>
+      <c r="D71">
+        <v>1466.299319250202</v>
+      </c>
+      <c r="E71">
+        <v>1279.844</v>
+      </c>
+      <c r="F71">
+        <v>2682.444</v>
+      </c>
+      <c r="G71">
+        <v>389.6</v>
+      </c>
+      <c r="H71">
+        <v>2485</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>363.8</v>
+      </c>
+      <c r="K71">
+        <v>170</v>
+      </c>
+      <c r="L71">
+        <v>193.8</v>
+      </c>
+      <c r="M71">
+        <v>640.5676272000001</v>
+      </c>
+      <c r="N71">
+        <v>-446.7676272</v>
+      </c>
+      <c r="O71">
+        <v>-107.224230528</v>
+      </c>
+      <c r="P71">
+        <v>-339.543396672</v>
+      </c>
+      <c r="Q71">
+        <v>-169.543396672</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2266593236820349</v>
+      </c>
+      <c r="T71">
+        <v>2.353126150359068</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.07261060038783053</v>
+      </c>
+      <c r="W71">
+        <v>0.2214605886273861</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.3025441682826272</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2250721964943272</v>
+      </c>
+      <c r="C72">
+        <v>-878.8917910432128</v>
+      </c>
+      <c r="D72">
+        <v>1452.828208956787</v>
+      </c>
+      <c r="E72">
+        <v>1318.72</v>
+      </c>
+      <c r="F72">
+        <v>2721.32</v>
+      </c>
+      <c r="G72">
+        <v>389.6</v>
+      </c>
+      <c r="H72">
+        <v>2485</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>363.8</v>
+      </c>
+      <c r="K72">
+        <v>170</v>
+      </c>
+      <c r="L72">
+        <v>193.8</v>
+      </c>
+      <c r="M72">
+        <v>649.851216</v>
+      </c>
+      <c r="N72">
+        <v>-456.051216</v>
+      </c>
+      <c r="O72">
+        <v>-109.45229184</v>
+      </c>
+      <c r="P72">
+        <v>-346.59892416</v>
+      </c>
+      <c r="Q72">
+        <v>-176.59892416</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2329213011381027</v>
+      </c>
+      <c r="T72">
+        <v>2.43156368870437</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.07157330609657581</v>
+      </c>
+      <c r="W72">
+        <v>0.2217082945041377</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.2982221087357325</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2270721964943272</v>
+      </c>
+      <c r="C73">
+        <v>-930.9936324639498</v>
+      </c>
+      <c r="D73">
+        <v>1439.60236753605</v>
+      </c>
+      <c r="E73">
+        <v>1357.596</v>
+      </c>
+      <c r="F73">
+        <v>2760.196</v>
+      </c>
+      <c r="G73">
+        <v>389.6</v>
+      </c>
+      <c r="H73">
+        <v>2485</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>363.8</v>
+      </c>
+      <c r="K73">
+        <v>170</v>
+      </c>
+      <c r="L73">
+        <v>193.8</v>
+      </c>
+      <c r="M73">
+        <v>659.1348048</v>
+      </c>
+      <c r="N73">
+        <v>-465.3348048</v>
+      </c>
+      <c r="O73">
+        <v>-111.680353152</v>
+      </c>
+      <c r="P73">
+        <v>-353.654451648</v>
+      </c>
+      <c r="Q73">
+        <v>-183.654451648</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.239615139108382</v>
+      </c>
+      <c r="T73">
+        <v>2.515410712452796</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.07056523136282122</v>
+      </c>
+      <c r="W73">
+        <v>0.2219490227505583</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.2940217973450884</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2290721964943272</v>
+      </c>
+      <c r="C74">
+        <v>-982.8568430085043</v>
+      </c>
+      <c r="D74">
+        <v>1426.615156991495</v>
+      </c>
+      <c r="E74">
+        <v>1396.472</v>
+      </c>
+      <c r="F74">
+        <v>2799.072</v>
+      </c>
+      <c r="G74">
+        <v>389.6</v>
+      </c>
+      <c r="H74">
+        <v>2485</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>363.8</v>
+      </c>
+      <c r="K74">
+        <v>170</v>
+      </c>
+      <c r="L74">
+        <v>193.8</v>
+      </c>
+      <c r="M74">
+        <v>668.4183935999999</v>
+      </c>
+      <c r="N74">
+        <v>-474.6183935999999</v>
+      </c>
+      <c r="O74">
+        <v>-113.908414464</v>
+      </c>
+      <c r="P74">
+        <v>-360.709979136</v>
+      </c>
+      <c r="Q74">
+        <v>-190.709979136</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2467871083622528</v>
+      </c>
+      <c r="T74">
+        <v>2.60524680932611</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.06958515870500426</v>
+      </c>
+      <c r="W74">
+        <v>0.222183064101245</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.2899381612708511</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2310721964943272</v>
+      </c>
+      <c r="C75">
+        <v>-1034.487823279245</v>
+      </c>
+      <c r="D75">
+        <v>1413.860176720755</v>
+      </c>
+      <c r="E75">
+        <v>1435.348</v>
+      </c>
+      <c r="F75">
+        <v>2837.948</v>
+      </c>
+      <c r="G75">
+        <v>389.6</v>
+      </c>
+      <c r="H75">
+        <v>2485</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>363.8</v>
+      </c>
+      <c r="K75">
+        <v>170</v>
+      </c>
+      <c r="L75">
+        <v>193.8</v>
+      </c>
+      <c r="M75">
+        <v>677.7019824</v>
+      </c>
+      <c r="N75">
+        <v>-483.9019824</v>
+      </c>
+      <c r="O75">
+        <v>-116.136475776</v>
+      </c>
+      <c r="P75">
+        <v>-367.765506624</v>
+      </c>
+      <c r="Q75">
+        <v>-197.765506624</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2544903345978918</v>
+      </c>
+      <c r="T75">
+        <v>2.701737431893744</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.06863193735288091</v>
+      </c>
+      <c r="W75">
+        <v>0.2224106933601321</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.2859664056370038</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2330721964943272</v>
+      </c>
+      <c r="C76">
+        <v>-1085.892747002757</v>
+      </c>
+      <c r="D76">
+        <v>1401.331252997243</v>
+      </c>
+      <c r="E76">
+        <v>1474.224</v>
+      </c>
+      <c r="F76">
+        <v>2876.824</v>
+      </c>
+      <c r="G76">
+        <v>389.6</v>
+      </c>
+      <c r="H76">
+        <v>2485</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>363.8</v>
+      </c>
+      <c r="K76">
+        <v>170</v>
+      </c>
+      <c r="L76">
+        <v>193.8</v>
+      </c>
+      <c r="M76">
+        <v>686.9855712000001</v>
+      </c>
+      <c r="N76">
+        <v>-493.1855712000001</v>
+      </c>
+      <c r="O76">
+        <v>-118.364537088</v>
+      </c>
+      <c r="P76">
+        <v>-374.8210341120001</v>
+      </c>
+      <c r="Q76">
+        <v>-204.8210341120001</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2627861166978107</v>
+      </c>
+      <c r="T76">
+        <v>2.805650410043503</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.06770447874000414</v>
+      </c>
+      <c r="W76">
+        <v>0.222632170476887</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.2821019947500172</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2350721964943272</v>
+      </c>
+      <c r="C77">
+        <v>-1137.077570993846</v>
+      </c>
+      <c r="D77">
+        <v>1389.022429006154</v>
+      </c>
+      <c r="E77">
+        <v>1513.1</v>
+      </c>
+      <c r="F77">
+        <v>2915.7</v>
+      </c>
+      <c r="G77">
+        <v>389.6</v>
+      </c>
+      <c r="H77">
+        <v>2485</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>363.8</v>
+      </c>
+      <c r="K77">
+        <v>170</v>
+      </c>
+      <c r="L77">
+        <v>193.8</v>
+      </c>
+      <c r="M77">
+        <v>696.2691599999999</v>
+      </c>
+      <c r="N77">
+        <v>-502.4691599999999</v>
+      </c>
+      <c r="O77">
+        <v>-120.5925984</v>
+      </c>
+      <c r="P77">
+        <v>-381.8765615999999</v>
+      </c>
+      <c r="Q77">
+        <v>-211.8765615999999</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2717455613657232</v>
+      </c>
+      <c r="T77">
+        <v>2.917876426445244</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.06680175235680408</v>
+      </c>
+      <c r="W77">
+        <v>0.2228477415371952</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.278340634820017</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2370721964943272</v>
+      </c>
+      <c r="C78">
+        <v>-1188.048044598991</v>
+      </c>
+      <c r="D78">
+        <v>1376.927955401009</v>
+      </c>
+      <c r="E78">
+        <v>1551.976</v>
+      </c>
+      <c r="F78">
+        <v>2954.576</v>
+      </c>
+      <c r="G78">
+        <v>389.6</v>
+      </c>
+      <c r="H78">
+        <v>2485</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>363.8</v>
+      </c>
+      <c r="K78">
+        <v>170</v>
+      </c>
+      <c r="L78">
+        <v>193.8</v>
+      </c>
+      <c r="M78">
+        <v>705.5527488</v>
+      </c>
+      <c r="N78">
+        <v>-511.7527488</v>
+      </c>
+      <c r="O78">
+        <v>-122.820659712</v>
+      </c>
+      <c r="P78">
+        <v>-388.932089088</v>
+      </c>
+      <c r="Q78">
+        <v>-218.932089088</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2814516264226283</v>
+      </c>
+      <c r="T78">
+        <v>3.039454610880462</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.06592278193105666</v>
+      </c>
+      <c r="W78">
+        <v>0.2230576396748637</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.2746782580460694</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2390721964943272</v>
+      </c>
+      <c r="C79">
+        <v>-1238.809718650705</v>
+      </c>
+      <c r="D79">
+        <v>1365.042281349296</v>
+      </c>
+      <c r="E79">
+        <v>1590.852</v>
+      </c>
+      <c r="F79">
+        <v>2993.452</v>
+      </c>
+      <c r="G79">
+        <v>389.6</v>
+      </c>
+      <c r="H79">
+        <v>2485</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>363.8</v>
+      </c>
+      <c r="K79">
+        <v>170</v>
+      </c>
+      <c r="L79">
+        <v>193.8</v>
+      </c>
+      <c r="M79">
+        <v>714.8363376000001</v>
+      </c>
+      <c r="N79">
+        <v>-521.0363376</v>
+      </c>
+      <c r="O79">
+        <v>-125.048721024</v>
+      </c>
+      <c r="P79">
+        <v>-395.9876165760001</v>
+      </c>
+      <c r="Q79">
+        <v>-225.9876165760001</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2920016971366556</v>
+      </c>
+      <c r="T79">
+        <v>3.171604811353526</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.065066641905978</v>
+      </c>
+      <c r="W79">
+        <v>0.2232620859128525</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.2711110079415751</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2410721964943272</v>
+      </c>
+      <c r="C80">
+        <v>-1289.367953962089</v>
+      </c>
+      <c r="D80">
+        <v>1353.360046037911</v>
+      </c>
+      <c r="E80">
+        <v>1629.728</v>
+      </c>
+      <c r="F80">
+        <v>3032.328</v>
+      </c>
+      <c r="G80">
+        <v>389.6</v>
+      </c>
+      <c r="H80">
+        <v>2485</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>363.8</v>
+      </c>
+      <c r="K80">
+        <v>170</v>
+      </c>
+      <c r="L80">
+        <v>193.8</v>
+      </c>
+      <c r="M80">
+        <v>724.1199264000001</v>
+      </c>
+      <c r="N80">
+        <v>-530.3199264</v>
+      </c>
+      <c r="O80">
+        <v>-127.276782336</v>
+      </c>
+      <c r="P80">
+        <v>-403.043144064</v>
+      </c>
+      <c r="Q80">
+        <v>-233.043144064</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3035108651883218</v>
+      </c>
+      <c r="T80">
+        <v>3.31576866641505</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.06423245418923469</v>
+      </c>
+      <c r="W80">
+        <v>0.2234612899396108</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.267635225788478</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2430721964943272</v>
+      </c>
+      <c r="C81">
+        <v>-1339.727929388916</v>
+      </c>
+      <c r="D81">
+        <v>1341.876070611084</v>
+      </c>
+      <c r="E81">
+        <v>1668.604</v>
+      </c>
+      <c r="F81">
+        <v>3071.204</v>
+      </c>
+      <c r="G81">
+        <v>389.6</v>
+      </c>
+      <c r="H81">
+        <v>2485</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>363.8</v>
+      </c>
+      <c r="K81">
+        <v>170</v>
+      </c>
+      <c r="L81">
+        <v>193.8</v>
+      </c>
+      <c r="M81">
+        <v>733.4035152000001</v>
+      </c>
+      <c r="N81">
+        <v>-539.6035152000002</v>
+      </c>
+      <c r="O81">
+        <v>-129.504843648</v>
+      </c>
+      <c r="P81">
+        <v>-410.0986715520002</v>
+      </c>
+      <c r="Q81">
+        <v>-240.0986715520002</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3161161444830038</v>
+      </c>
+      <c r="T81">
+        <v>3.473662412434814</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.06341938514886462</v>
+      </c>
+      <c r="W81">
+        <v>0.2236554508264511</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.2642474381202692</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2450721964943272</v>
+      </c>
+      <c r="C82">
+        <v>-1389.894649484687</v>
+      </c>
+      <c r="D82">
+        <v>1330.585350515313</v>
+      </c>
+      <c r="E82">
+        <v>1707.48</v>
+      </c>
+      <c r="F82">
+        <v>3110.08</v>
+      </c>
+      <c r="G82">
+        <v>389.6</v>
+      </c>
+      <c r="H82">
+        <v>2485</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>363.8</v>
+      </c>
+      <c r="K82">
+        <v>170</v>
+      </c>
+      <c r="L82">
+        <v>193.8</v>
+      </c>
+      <c r="M82">
+        <v>742.687104</v>
+      </c>
+      <c r="N82">
+        <v>-548.8871039999999</v>
+      </c>
+      <c r="O82">
+        <v>-131.73290496</v>
+      </c>
+      <c r="P82">
+        <v>-417.1541990399999</v>
+      </c>
+      <c r="Q82">
+        <v>-247.1541990399999</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.329981951707154</v>
+      </c>
+      <c r="T82">
+        <v>3.647345533056555</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.06262664283450382</v>
+      </c>
+      <c r="W82">
+        <v>0.2238447576911205</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.2609443451437661</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2470721964943272</v>
+      </c>
+      <c r="C83">
+        <v>-1439.872951772459</v>
+      </c>
+      <c r="D83">
+        <v>1319.483048227541</v>
+      </c>
+      <c r="E83">
+        <v>1746.356</v>
+      </c>
+      <c r="F83">
+        <v>3148.956</v>
+      </c>
+      <c r="G83">
+        <v>389.6</v>
+      </c>
+      <c r="H83">
+        <v>2485</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>363.8</v>
+      </c>
+      <c r="K83">
+        <v>170</v>
+      </c>
+      <c r="L83">
+        <v>193.8</v>
+      </c>
+      <c r="M83">
+        <v>751.9706928000001</v>
+      </c>
+      <c r="N83">
+        <v>-558.1706928000001</v>
+      </c>
+      <c r="O83">
+        <v>-133.960966272</v>
+      </c>
+      <c r="P83">
+        <v>-424.2097265280001</v>
+      </c>
+      <c r="Q83">
+        <v>-254.2097265280001</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.345307317586478</v>
+      </c>
+      <c r="T83">
+        <v>3.839311087427953</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.06185347440444822</v>
+      </c>
+      <c r="W83">
+        <v>0.2240293903122178</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.2577228100185341</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2490721964943272</v>
+      </c>
+      <c r="C84">
+        <v>-1489.667513655627</v>
+      </c>
+      <c r="D84">
+        <v>1308.564486344373</v>
+      </c>
+      <c r="E84">
+        <v>1785.232</v>
+      </c>
+      <c r="F84">
+        <v>3187.832</v>
+      </c>
+      <c r="G84">
+        <v>389.6</v>
+      </c>
+      <c r="H84">
+        <v>2485</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>363.8</v>
+      </c>
+      <c r="K84">
+        <v>170</v>
+      </c>
+      <c r="L84">
+        <v>193.8</v>
+      </c>
+      <c r="M84">
+        <v>761.2542816000001</v>
+      </c>
+      <c r="N84">
+        <v>-567.4542816000001</v>
+      </c>
+      <c r="O84">
+        <v>-136.189027584</v>
+      </c>
+      <c r="P84">
+        <v>-431.2652540160001</v>
+      </c>
+      <c r="Q84">
+        <v>-261.2652540160001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3623355018968378</v>
+      </c>
+      <c r="T84">
+        <v>4.052606147840617</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.06109916374097934</v>
+      </c>
+      <c r="W84">
+        <v>0.2242095196986541</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.2545798489207474</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2510721964943272</v>
+      </c>
+      <c r="C85">
+        <v>-1539.282858988408</v>
+      </c>
+      <c r="D85">
+        <v>1297.825141011592</v>
+      </c>
+      <c r="E85">
+        <v>1824.108</v>
+      </c>
+      <c r="F85">
+        <v>3226.708</v>
+      </c>
+      <c r="G85">
+        <v>389.6</v>
+      </c>
+      <c r="H85">
+        <v>2485</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>363.8</v>
+      </c>
+      <c r="K85">
+        <v>170</v>
+      </c>
+      <c r="L85">
+        <v>193.8</v>
+      </c>
+      <c r="M85">
+        <v>770.5378704000001</v>
+      </c>
+      <c r="N85">
+        <v>-576.7378704</v>
+      </c>
+      <c r="O85">
+        <v>-138.417088896</v>
+      </c>
+      <c r="P85">
+        <v>-438.320781504</v>
+      </c>
+      <c r="Q85">
+        <v>-268.320781504</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.3813670020084166</v>
+      </c>
+      <c r="T85">
+        <v>4.290994744772418</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.06036302923807598</v>
+      </c>
+      <c r="W85">
+        <v>0.2243853086179474</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.2515126218253166</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2530721964943272</v>
+      </c>
+      <c r="C86">
+        <v>-1588.723364325416</v>
+      </c>
+      <c r="D86">
+        <v>1287.260635674583</v>
+      </c>
+      <c r="E86">
+        <v>1862.984</v>
+      </c>
+      <c r="F86">
+        <v>3265.584</v>
+      </c>
+      <c r="G86">
+        <v>389.6</v>
+      </c>
+      <c r="H86">
+        <v>2485</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>363.8</v>
+      </c>
+      <c r="K86">
+        <v>170</v>
+      </c>
+      <c r="L86">
+        <v>193.8</v>
+      </c>
+      <c r="M86">
+        <v>779.8214592</v>
+      </c>
+      <c r="N86">
+        <v>-586.0214592</v>
+      </c>
+      <c r="O86">
+        <v>-140.645150208</v>
+      </c>
+      <c r="P86">
+        <v>-445.376308992</v>
+      </c>
+      <c r="Q86">
+        <v>-275.376308992</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4027774396339425</v>
+      </c>
+      <c r="T86">
+        <v>4.559181916320693</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.0596444217471465</v>
+      </c>
+      <c r="W86">
+        <v>0.2245569120867814</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.2485184239464439</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2550721964943272</v>
+      </c>
+      <c r="C87">
+        <v>-1637.993264868468</v>
+      </c>
+      <c r="D87">
+        <v>1276.866735131533</v>
+      </c>
+      <c r="E87">
+        <v>1901.86</v>
+      </c>
+      <c r="F87">
+        <v>3304.46</v>
+      </c>
+      <c r="G87">
+        <v>389.6</v>
+      </c>
+      <c r="H87">
+        <v>2485</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>363.8</v>
+      </c>
+      <c r="K87">
+        <v>170</v>
+      </c>
+      <c r="L87">
+        <v>193.8</v>
+      </c>
+      <c r="M87">
+        <v>789.105048</v>
+      </c>
+      <c r="N87">
+        <v>-595.3050479999999</v>
+      </c>
+      <c r="O87">
+        <v>-142.87321152</v>
+      </c>
+      <c r="P87">
+        <v>-452.43183648</v>
+      </c>
+      <c r="Q87">
+        <v>-282.43183648</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.4270426022762052</v>
+      </c>
+      <c r="T87">
+        <v>4.863127377408738</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.05894272266776831</v>
+      </c>
+      <c r="W87">
+        <v>0.2247244778269369</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.245594677782368</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2570721964943272</v>
+      </c>
+      <c r="C88">
+        <v>-1687.096660127587</v>
+      </c>
+      <c r="D88">
+        <v>1266.639339872413</v>
+      </c>
+      <c r="E88">
+        <v>1940.736</v>
+      </c>
+      <c r="F88">
+        <v>3343.336</v>
+      </c>
+      <c r="G88">
+        <v>389.6</v>
+      </c>
+      <c r="H88">
+        <v>2485</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>363.8</v>
+      </c>
+      <c r="K88">
+        <v>170</v>
+      </c>
+      <c r="L88">
+        <v>193.8</v>
+      </c>
+      <c r="M88">
+        <v>798.3886368</v>
+      </c>
+      <c r="N88">
+        <v>-604.5886367999999</v>
+      </c>
+      <c r="O88">
+        <v>-145.101272832</v>
+      </c>
+      <c r="P88">
+        <v>-459.487363968</v>
+      </c>
+      <c r="Q88">
+        <v>-289.487363968</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.4547742167245056</v>
+      </c>
+      <c r="T88">
+        <v>5.21049361865222</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.05825734217163147</v>
+      </c>
+      <c r="W88">
+        <v>0.2248881466894144</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.2427389257151312</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2590721964943272</v>
+      </c>
+      <c r="C89">
+        <v>-1736.037519312124</v>
+      </c>
+      <c r="D89">
+        <v>1256.574480687876</v>
+      </c>
+      <c r="E89">
+        <v>1979.612</v>
+      </c>
+      <c r="F89">
+        <v>3382.212</v>
+      </c>
+      <c r="G89">
+        <v>389.6</v>
+      </c>
+      <c r="H89">
+        <v>2485</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>363.8</v>
+      </c>
+      <c r="K89">
+        <v>170</v>
+      </c>
+      <c r="L89">
+        <v>193.8</v>
+      </c>
+      <c r="M89">
+        <v>807.6722256</v>
+      </c>
+      <c r="N89">
+        <v>-613.8722256000001</v>
+      </c>
+      <c r="O89">
+        <v>-147.329334144</v>
+      </c>
+      <c r="P89">
+        <v>-466.5428914560001</v>
+      </c>
+      <c r="Q89">
+        <v>-296.5428914560001</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.4867722333956214</v>
+      </c>
+      <c r="T89">
+        <v>5.611300820087006</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.05758771754896903</v>
+      </c>
+      <c r="W89">
+        <v>0.2250480530493062</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.2399488231207042</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2610721964943272</v>
+      </c>
+      <c r="C90">
+        <v>-1784.819686466855</v>
+      </c>
+      <c r="D90">
+        <v>1246.668313533145</v>
+      </c>
+      <c r="E90">
+        <v>2018.488</v>
+      </c>
+      <c r="F90">
+        <v>3421.088</v>
+      </c>
+      <c r="G90">
+        <v>389.6</v>
+      </c>
+      <c r="H90">
+        <v>2485</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>363.8</v>
+      </c>
+      <c r="K90">
+        <v>170</v>
+      </c>
+      <c r="L90">
+        <v>193.8</v>
+      </c>
+      <c r="M90">
+        <v>816.9558144</v>
+      </c>
+      <c r="N90">
+        <v>-623.1558144000001</v>
+      </c>
+      <c r="O90">
+        <v>-149.557395456</v>
+      </c>
+      <c r="P90">
+        <v>-473.5984189440001</v>
+      </c>
+      <c r="Q90">
+        <v>-303.5984189440001</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.5241032528452567</v>
+      </c>
+      <c r="T90">
+        <v>6.078909221760925</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.05693331166773075</v>
+      </c>
+      <c r="W90">
+        <v>0.2252043251737459</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.2372221319488781</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2630721964943272</v>
+      </c>
+      <c r="C91">
+        <v>-1833.446885367054</v>
+      </c>
+      <c r="D91">
+        <v>1236.917114632946</v>
+      </c>
+      <c r="E91">
+        <v>2057.364</v>
+      </c>
+      <c r="F91">
+        <v>3459.964</v>
+      </c>
+      <c r="G91">
+        <v>389.6</v>
+      </c>
+      <c r="H91">
+        <v>2485</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>363.8</v>
+      </c>
+      <c r="K91">
+        <v>170</v>
+      </c>
+      <c r="L91">
+        <v>193.8</v>
+      </c>
+      <c r="M91">
+        <v>826.2394032000001</v>
+      </c>
+      <c r="N91">
+        <v>-632.4394032</v>
+      </c>
+      <c r="O91">
+        <v>-151.785456768</v>
+      </c>
+      <c r="P91">
+        <v>-480.653946432</v>
+      </c>
+      <c r="Q91">
+        <v>-310.653946432</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.5682217303766437</v>
+      </c>
+      <c r="T91">
+        <v>6.631537332830099</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.05629361153663266</v>
+      </c>
+      <c r="W91">
+        <v>0.2253570855650521</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.2345567147359695</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2650721964943272</v>
+      </c>
+      <c r="C92">
+        <v>-1881.922724185609</v>
+      </c>
+      <c r="D92">
+        <v>1227.317275814391</v>
+      </c>
+      <c r="E92">
+        <v>2096.24</v>
+      </c>
+      <c r="F92">
+        <v>3498.84</v>
+      </c>
+      <c r="G92">
+        <v>389.6</v>
+      </c>
+      <c r="H92">
+        <v>2485</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>363.8</v>
+      </c>
+      <c r="K92">
+        <v>170</v>
+      </c>
+      <c r="L92">
+        <v>193.8</v>
+      </c>
+      <c r="M92">
+        <v>835.522992</v>
+      </c>
+      <c r="N92">
+        <v>-641.722992</v>
+      </c>
+      <c r="O92">
+        <v>-154.01351808</v>
+      </c>
+      <c r="P92">
+        <v>-487.70947392</v>
+      </c>
+      <c r="Q92">
+        <v>-317.70947392</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.6211639034143082</v>
+      </c>
+      <c r="T92">
+        <v>7.294691066113111</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.0556681269640034</v>
+      </c>
+      <c r="W92">
+        <v>0.225506451280996</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.2319505290166809</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2670721964943272</v>
+      </c>
+      <c r="C93">
+        <v>-1930.250699944479</v>
+      </c>
+      <c r="D93">
+        <v>1217.865300055521</v>
+      </c>
+      <c r="E93">
+        <v>2135.116</v>
+      </c>
+      <c r="F93">
+        <v>3537.716</v>
+      </c>
+      <c r="G93">
+        <v>389.6</v>
+      </c>
+      <c r="H93">
+        <v>2485</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>363.8</v>
+      </c>
+      <c r="K93">
+        <v>170</v>
+      </c>
+      <c r="L93">
+        <v>193.8</v>
+      </c>
+      <c r="M93">
+        <v>844.8065808</v>
+      </c>
+      <c r="N93">
+        <v>-651.0065807999999</v>
+      </c>
+      <c r="O93">
+        <v>-156.241579392</v>
+      </c>
+      <c r="P93">
+        <v>-494.765001408</v>
+      </c>
+      <c r="Q93">
+        <v>-324.765001408</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.6858710037936757</v>
+      </c>
+      <c r="T93">
+        <v>8.105212295681234</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.05505638930505832</v>
+      </c>
+      <c r="W93">
+        <v>0.2256525342339521</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.2294016221044097</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2690721964943272</v>
+      </c>
+      <c r="C94">
+        <v>-1978.434202762043</v>
+      </c>
+      <c r="D94">
+        <v>1208.557797237957</v>
+      </c>
+      <c r="E94">
+        <v>2173.992</v>
+      </c>
+      <c r="F94">
+        <v>3576.592</v>
+      </c>
+      <c r="G94">
+        <v>389.6</v>
+      </c>
+      <c r="H94">
+        <v>2485</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>363.8</v>
+      </c>
+      <c r="K94">
+        <v>170</v>
+      </c>
+      <c r="L94">
+        <v>193.8</v>
+      </c>
+      <c r="M94">
+        <v>854.0901696000001</v>
+      </c>
+      <c r="N94">
+        <v>-660.2901696000001</v>
+      </c>
+      <c r="O94">
+        <v>-158.469640704</v>
+      </c>
+      <c r="P94">
+        <v>-501.8205288960001</v>
+      </c>
+      <c r="Q94">
+        <v>-331.8205288960001</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.7667548792678853</v>
+      </c>
+      <c r="T94">
+        <v>9.118363832641391</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.05445795029087289</v>
+      </c>
+      <c r="W94">
+        <v>0.2257954414705396</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.2269081262119703</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2710721964943272</v>
+      </c>
+      <c r="C95">
+        <v>-2026.476519907148</v>
+      </c>
+      <c r="D95">
+        <v>1199.391480092852</v>
+      </c>
+      <c r="E95">
+        <v>2212.868</v>
+      </c>
+      <c r="F95">
+        <v>3615.468</v>
+      </c>
+      <c r="G95">
+        <v>389.6</v>
+      </c>
+      <c r="H95">
+        <v>2485</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>363.8</v>
+      </c>
+      <c r="K95">
+        <v>170</v>
+      </c>
+      <c r="L95">
+        <v>193.8</v>
+      </c>
+      <c r="M95">
+        <v>863.3737584000002</v>
+      </c>
+      <c r="N95">
+        <v>-669.5737584000001</v>
+      </c>
+      <c r="O95">
+        <v>-160.697702016</v>
+      </c>
+      <c r="P95">
+        <v>-508.8760563840001</v>
+      </c>
+      <c r="Q95">
+        <v>-338.8760563840001</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.8707484334490121</v>
+      </c>
+      <c r="T95">
+        <v>10.42098723730445</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.05387238093290651</v>
+      </c>
+      <c r="W95">
+        <v>0.2259352754332219</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.2244682538871106</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2730721964943272</v>
+      </c>
+      <c r="C96">
+        <v>-2074.380839670066</v>
+      </c>
+      <c r="D96">
+        <v>1190.363160329934</v>
+      </c>
+      <c r="E96">
+        <v>2251.744</v>
+      </c>
+      <c r="F96">
+        <v>3654.344</v>
+      </c>
+      <c r="G96">
+        <v>389.6</v>
+      </c>
+      <c r="H96">
+        <v>2485</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>363.8</v>
+      </c>
+      <c r="K96">
+        <v>170</v>
+      </c>
+      <c r="L96">
+        <v>193.8</v>
+      </c>
+      <c r="M96">
+        <v>872.6573472</v>
+      </c>
+      <c r="N96">
+        <v>-678.8573472</v>
+      </c>
+      <c r="O96">
+        <v>-162.925763328</v>
+      </c>
+      <c r="P96">
+        <v>-515.931583872</v>
+      </c>
+      <c r="Q96">
+        <v>-345.931583872</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.009406505690514</v>
+      </c>
+      <c r="T96">
+        <v>12.15781844352186</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.05329927049745007</v>
+      </c>
+      <c r="W96">
+        <v>0.2260721342052089</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.2220802937393752</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2750721964943272</v>
+      </c>
+      <c r="C97">
+        <v>-2122.150255059933</v>
+      </c>
+      <c r="D97">
+        <v>1181.469744940067</v>
+      </c>
+      <c r="E97">
+        <v>2290.62</v>
+      </c>
+      <c r="F97">
+        <v>3693.22</v>
+      </c>
+      <c r="G97">
+        <v>389.6</v>
+      </c>
+      <c r="H97">
+        <v>2485</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>363.8</v>
+      </c>
+      <c r="K97">
+        <v>170</v>
+      </c>
+      <c r="L97">
+        <v>193.8</v>
+      </c>
+      <c r="M97">
+        <v>881.9409360000001</v>
+      </c>
+      <c r="N97">
+        <v>-688.140936</v>
+      </c>
+      <c r="O97">
+        <v>-165.15382464</v>
+      </c>
+      <c r="P97">
+        <v>-522.98711136</v>
+      </c>
+      <c r="Q97">
+        <v>-352.98711136</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.203527806828617</v>
+      </c>
+      <c r="T97">
+        <v>14.58938213222624</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.05273822554484533</v>
+      </c>
+      <c r="W97">
+        <v>0.2262061117398909</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.2197426064368556</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2770721964943272</v>
+      </c>
+      <c r="C98">
+        <v>-2169.787767337657</v>
+      </c>
+      <c r="D98">
+        <v>1172.708232662342</v>
+      </c>
+      <c r="E98">
+        <v>2329.496</v>
+      </c>
+      <c r="F98">
+        <v>3732.096</v>
+      </c>
+      <c r="G98">
+        <v>389.6</v>
+      </c>
+      <c r="H98">
+        <v>2485</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>363.8</v>
+      </c>
+      <c r="K98">
+        <v>170</v>
+      </c>
+      <c r="L98">
+        <v>193.8</v>
+      </c>
+      <c r="M98">
+        <v>891.2245247999999</v>
+      </c>
+      <c r="N98">
+        <v>-697.4245248</v>
+      </c>
+      <c r="O98">
+        <v>-167.381885952</v>
+      </c>
+      <c r="P98">
+        <v>-530.042638848</v>
+      </c>
+      <c r="Q98">
+        <v>-360.042638848</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.494709758535768</v>
+      </c>
+      <c r="T98">
+        <v>18.23672766528276</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.0521888690287532</v>
+      </c>
+      <c r="W98">
+        <v>0.2263372980759338</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.2174536209531382</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2790721964943272</v>
+      </c>
+      <c r="C99">
+        <v>-2217.296289392807</v>
+      </c>
+      <c r="D99">
+        <v>1164.075710607192</v>
+      </c>
+      <c r="E99">
+        <v>2368.372</v>
+      </c>
+      <c r="F99">
+        <v>3770.972</v>
+      </c>
+      <c r="G99">
+        <v>389.6</v>
+      </c>
+      <c r="H99">
+        <v>2485</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>363.8</v>
+      </c>
+      <c r="K99">
+        <v>170</v>
+      </c>
+      <c r="L99">
+        <v>193.8</v>
+      </c>
+      <c r="M99">
+        <v>900.5081136</v>
+      </c>
+      <c r="N99">
+        <v>-706.7081135999999</v>
+      </c>
+      <c r="O99">
+        <v>-169.609947264</v>
+      </c>
+      <c r="P99">
+        <v>-537.098166336</v>
+      </c>
+      <c r="Q99">
+        <v>-367.098166336</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.980013011381025</v>
+      </c>
+      <c r="T99">
+        <v>24.31563688704368</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.05165083945113718</v>
+      </c>
+      <c r="W99">
+        <v>0.2264657795390685</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.215211831046405</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2810721964943272</v>
+      </c>
+      <c r="C100">
+        <v>-2264.678648972422</v>
+      </c>
+      <c r="D100">
+        <v>1155.569351027578</v>
+      </c>
+      <c r="E100">
+        <v>2407.248</v>
+      </c>
+      <c r="F100">
+        <v>3809.848</v>
+      </c>
+      <c r="G100">
+        <v>389.6</v>
+      </c>
+      <c r="H100">
+        <v>2485</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>363.8</v>
+      </c>
+      <c r="K100">
+        <v>170</v>
+      </c>
+      <c r="L100">
+        <v>193.8</v>
+      </c>
+      <c r="M100">
+        <v>909.7917024000001</v>
+      </c>
+      <c r="N100">
+        <v>-715.9917024000001</v>
+      </c>
+      <c r="O100">
+        <v>-171.838008576</v>
+      </c>
+      <c r="P100">
+        <v>-544.1536938240001</v>
+      </c>
+      <c r="Q100">
+        <v>-374.1536938240001</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.950619517071537</v>
+      </c>
+      <c r="T100">
+        <v>36.47345533056551</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.05112379006898271</v>
+      </c>
+      <c r="W100">
+        <v>0.226591638931527</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.2130157919540946</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2830721964943272</v>
+      </c>
+      <c r="C101">
+        <v>-2311.937591769301</v>
+      </c>
+      <c r="D101">
+        <v>1147.186408230699</v>
+      </c>
+      <c r="E101">
+        <v>2446.124</v>
+      </c>
+      <c r="F101">
+        <v>3848.724</v>
+      </c>
+      <c r="G101">
+        <v>389.6</v>
+      </c>
+      <c r="H101">
+        <v>2485</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>363.8</v>
+      </c>
+      <c r="K101">
+        <v>170</v>
+      </c>
+      <c r="L101">
+        <v>193.8</v>
+      </c>
+      <c r="M101">
+        <v>919.0752911999999</v>
+      </c>
+      <c r="N101">
+        <v>-725.2752911999999</v>
+      </c>
+      <c r="O101">
+        <v>-174.066069888</v>
+      </c>
+      <c r="P101">
+        <v>-551.209221312</v>
+      </c>
+      <c r="Q101">
+        <v>-381.209221312</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>5.862439034143074</v>
+      </c>
+      <c r="T101">
+        <v>72.94691066113103</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.050607388149094</v>
+      </c>
+      <c r="W101">
+        <v>0.2267149557099964</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.2108641172878918</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
